--- a/מערכות שעות - גורדון.xlsx
+++ b/מערכות שעות - גורדון.xlsx
@@ -914,27 +914,29 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
+          <t>אנה
+ פינת חי · + אבי קרן צבי</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>תל"ן · חגית + יפעת</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
           <t>אנה</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>תל"ן · חגית + יפעת</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>אנה</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>אנה</t>
-        </is>
-      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>אנה</t>
+          <t>אנה
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1117,7 +1119,8 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>פנינה</t>
+          <t>פנינה
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1221,7 +1224,8 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>פנינה</t>
+          <t>פנינה
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1503,7 +1507,8 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>טלי</t>
+          <t>טלי
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1531,7 +1536,8 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>אביטל</t>
+          <t>אביטל
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1706,7 +1712,8 @@
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>יערה</t>
+          <t>יערה
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
@@ -1810,7 +1817,8 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>שחר</t>
+          <t>שחר
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -2003,7 +2011,8 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>דניאל</t>
+          <t>דניאל
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -2090,7 +2099,8 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>לייה</t>
+          <t>לייה
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="I48" s="3" t="n"/>
@@ -2187,7 +2197,8 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>צופיה</t>
+          <t>צופיה
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -2208,7 +2219,8 @@
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>אנה</t>
+          <t>אנה
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -2507,7 +2519,8 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>דניאל</t>
+          <t>דניאל
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -2594,7 +2607,8 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>דניאל</t>
+          <t>דניאל
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -5897,7 +5911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C1:I417"/>
+  <dimension ref="C1:I428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5915,7 +5929,7 @@
     <row r="1">
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה אביטל בוארון</t>
+          <t>מערכת שעות למורה אבי קרן צבי</t>
         </is>
       </c>
     </row>
@@ -5978,31 +5992,25 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>חצי כיתה עם הילית
- ב אביטל</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
+          <t>פינת חי
+ ג דליה</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
+          <t>פינת חי
+ א פנינה</t>
         </is>
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
+          <t>פינת חי
+ ג דליה</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="C5" s="2" t="inlineStr">
@@ -6011,33 +6019,22 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>חצי כיתה עם יפעת
- ב אביטל</t>
+          <t>פינת חי
+ ג דניאל</t>
         </is>
       </c>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
+          <t>פינת חי
+ ב יערה</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="C6" s="2" t="inlineStr">
@@ -6048,30 +6045,25 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>◦ הדרכת שפה (קטיה)</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
+          <t>פינת חי
+ א אנה</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
+          <t>פינת חי
+ ג לייה</t>
         </is>
       </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
+          <t>פינת חי
+ א אנה</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="C7" s="2" t="inlineStr">
@@ -6082,30 +6074,25 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+          <t>פינת חי
+ א פנינה</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>ג לייה</t>
+          <t>פינת חי
+ ב אביטל</t>
         </is>
       </c>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
+          <t>פינת חי
+ ג דניאל</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="C8" s="2" t="inlineStr">
@@ -6116,23 +6103,22 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
+          <t>פינת חי
+ ב אביטל</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
+          <t>פינת חי
+ ב יערה</t>
         </is>
       </c>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
+          <t>פינת חי
+ ג לייה</t>
         </is>
       </c>
       <c r="I8" s="3" t="n"/>
@@ -6149,16 +6135,8 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
@@ -6184,7 +6162,7 @@
     <row r="12">
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה אופיר</t>
+          <t>מערכת שעות למורה אביטל בוארון</t>
         </is>
       </c>
     </row>
@@ -6245,12 +6223,33 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>חצי כיתה עם הילית
+ ב אביטל</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
       <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="C16" s="2" t="inlineStr">
@@ -6259,16 +6258,33 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>ו שרית</t>
+          <t>חצי כיתה עם יפעת
+ ב אביטל</t>
         </is>
       </c>
       <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="C17" s="2" t="inlineStr">
@@ -6277,17 +6293,32 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>◦ הדרכת שפה (קטיה)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>מגמת חדשנות וטכנולוגיה
- במקביל: חסן (ליווי מגמה ימית) · חגית (אומנויות) · יעל (בישול וספורט אתגרי)</t>
+          <t>ב אביטל</t>
         </is>
       </c>
       <c r="G17" s="3" t="n"/>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="C18" s="2" t="inlineStr">
@@ -6296,17 +6327,32 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>מגמת חדשנות וטכנולוגיה
- במקביל: חסן (ליווי מגמה ימית) · חגית (אומנויות) · יעל (בישול וספורט אתגרי)</t>
+          <t>ג לייה</t>
         </is>
       </c>
       <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="C19" s="2" t="inlineStr">
@@ -6315,15 +6361,27 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>ו אורנה</t>
+          <t>◦ מפגשה (מעגלי שיח)</t>
         </is>
       </c>
       <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
       <c r="I19" s="3" t="n"/>
     </row>
     <row r="20">
@@ -6338,10 +6396,14 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E20" s="3" t="n"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>ו שרית</t>
+          <t>◦ מפגשה (מעגלי שיח)</t>
         </is>
       </c>
       <c r="G20" s="3" t="n"/>
@@ -6369,7 +6431,7 @@
     <row r="23">
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה אורנה לוי</t>
+          <t>מערכת שעות למורה אופיר</t>
         </is>
       </c>
     </row>
@@ -6430,28 +6492,12 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>◦ הדרכת עברית (קטיה)</t>
-        </is>
-      </c>
+      <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
+      <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
+      <c r="H26" s="3" t="n"/>
+      <c r="I26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="C27" s="2" t="inlineStr">
@@ -6460,28 +6506,16 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
+      <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>ו אורנה</t>
+          <t>ו שרית</t>
         </is>
       </c>
       <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
+      <c r="H27" s="3" t="n"/>
+      <c r="I27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="C28" s="2" t="inlineStr">
@@ -6490,28 +6524,17 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
+      <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>ו אורנה</t>
+          <t>מגמת חדשנות וטכנולוגיה
+ במקביל: חסן (ליווי מגמה ימית) · חגית (אומנויות) · יעל (בישול וספורט אתגרי)</t>
         </is>
       </c>
       <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
+      <c r="H28" s="3" t="n"/>
+      <c r="I28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="C29" s="2" t="inlineStr">
@@ -6520,28 +6543,17 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
+      <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>ו אורנה</t>
+          <t>מגמת חדשנות וטכנולוגיה
+ במקביל: חסן (ליווי מגמה ימית) · חגית (אומנויות) · יעל (בישול וספורט אתגרי)</t>
         </is>
       </c>
       <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="C30" s="2" t="inlineStr">
@@ -6550,23 +6562,15 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
+      <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n"/>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
+          <t>ו אורנה</t>
         </is>
       </c>
       <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
+      <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
     </row>
     <row r="31">
@@ -6584,7 +6588,7 @@
       <c r="E31" s="3" t="n"/>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
+          <t>ו שרית</t>
         </is>
       </c>
       <c r="G31" s="3" t="n"/>
@@ -6612,7 +6616,7 @@
     <row r="34">
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה אינס אלקבץ</t>
+          <t>מערכת שעות למורה אורנה לוי</t>
         </is>
       </c>
     </row>
@@ -6675,29 +6679,24 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n"/>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
+          <t>◦ הדרכת עברית (קטיה)</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n"/>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>חצי כיתה עם יעל
- ד אינס</t>
+          <t>ו אורנה</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>ד אינס</t>
+          <t>ו אורנה</t>
         </is>
       </c>
     </row>
@@ -6710,30 +6709,24 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>חצי כיתה עם חגית
- ד אינס</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n"/>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n"/>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>חצי כיתה עם יעל
- ד אינס</t>
+          <t>ו אורנה</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>ד אינס</t>
+          <t>ו אורנה</t>
         </is>
       </c>
     </row>
@@ -6746,29 +6739,24 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>חצי כיתה עם חגית
- ד אינס</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="n"/>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>ו שרית</t>
+          <t>ו אורנה</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>ד אינס</t>
+          <t>ו אורנה</t>
         </is>
       </c>
     </row>
@@ -6781,28 +6769,24 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n"/>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
+          <t>ו אורנה</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>ד אינס</t>
+          <t>ו אורנה</t>
         </is>
       </c>
     </row>
@@ -6815,23 +6799,19 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n"/>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n"/>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
+          <t>ו אורנה</t>
         </is>
       </c>
       <c r="I41" s="3" t="n"/>
@@ -6848,17 +6828,13 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="n"/>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
+      <c r="E42" s="3" t="n"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n"/>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
     </row>
@@ -6883,7 +6859,7 @@
     <row r="45">
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה אלי אליהו מור</t>
+          <t>מערכת שעות למורה אינס אלקבץ</t>
         </is>
       </c>
     </row>
@@ -6946,30 +6922,31 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>גיאוגרפיה
- ח גלית</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך
- ז נעמי</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="F48" s="3" t="n"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה
- ז אלי</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה
- ח גלית</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="n"/>
+          <t>חצי כיתה עם יעל
+ ד אינס</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>ד אינס</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="C49" s="2" t="inlineStr">
@@ -6978,27 +6955,34 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n"/>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>חצי כיתה עם חגית
+ ד אינס</t>
+        </is>
+      </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך
- ז נעמי</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="F49" s="3" t="n"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה
- ז נעמי</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה
- ח גלית</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="n"/>
+          <t>חצי כיתה עם יעל
+ ד אינס</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>ד אינס</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="C50" s="2" t="inlineStr">
@@ -7009,34 +6993,31 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה
- ז נעמי</t>
+          <t>חצי כיתה עם חגית
+ ד אינס</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה
- ז נעמי</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr">
-        <is>
-          <t>◦ ישיבת מרכזי בית חינוך</t>
-        </is>
-      </c>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>גיאוגרפיה
- ח גלית</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>מגמת יזמות
- במקביל: מאמי (אומנות בתנועה) · יעל (תזונה) · תמיר (ליווי כדורעף)</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="n"/>
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>ד אינס</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="C51" s="2" t="inlineStr">
@@ -7045,31 +7026,32 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D51" s="3" t="n"/>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>ו שרית</t>
+        </is>
+      </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה
- ז נעמי</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>◦ ישיבת מרכזי בית חינוך</t>
-        </is>
-      </c>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה
- ז אלי</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>מגמת יזמות
- במקביל: מאמי (אומנות בתנועה) · יעל (תזונה) · תמיר (ליווי כדורעף)</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="n"/>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>ד אינס</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="C52" s="2" t="inlineStr">
@@ -7080,27 +7062,23 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך
- ז אלי</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה
- ז אלי</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>חינוך
- ז אלי / ◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="n"/>
+          <t>ד אינס</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>חינוך
- ז אלי</t>
+          <t>ה תניה</t>
         </is>
       </c>
       <c r="I52" s="3" t="n"/>
@@ -7119,18 +7097,13 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך
- ז אלי</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
+          <t>ד מירי</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>◦ ישיבת צוות חטיבה</t>
+          <t>ה דני</t>
         </is>
       </c>
       <c r="H53" s="3" t="n"/>
@@ -7148,12 +7121,7 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>היסטוריה
- ז אלי</t>
-        </is>
-      </c>
+      <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="n"/>
       <c r="G54" s="3" t="n"/>
       <c r="H54" s="3" t="n"/>
@@ -7162,7 +7130,7 @@
     <row r="56">
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה אנה זטרברג</t>
+          <t>מערכת שעות למורה אלי אליהו מור</t>
         </is>
       </c>
     </row>
@@ -7225,28 +7193,27 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>גיאוגרפיה
+ ח גלית</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>עם צופיה
- א אנה</t>
-        </is>
-      </c>
+          <t>תנ"ך
+ ז נעמי</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>היסטוריה
+ ז אלי</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>היסטוריה
+ ח גלית</t>
         </is>
       </c>
       <c r="I59" s="3" t="n"/>
@@ -7258,30 +7225,24 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>◦ הדרכת שפה (קטיה)</t>
-        </is>
-      </c>
+      <c r="D60" s="3" t="n"/>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>עם צופיה
- א אנה</t>
-        </is>
-      </c>
+          <t>תנ"ך
+ ז נעמי</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>היסטוריה
+ ז נעמי</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>היסטוריה
+ ח גלית</t>
         </is>
       </c>
       <c r="I60" s="3" t="n"/>
@@ -7295,27 +7256,31 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>היסטוריה
+ ז נעמי</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
+          <t>היסטוריה
+ ז נעמי</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>◦ ישיבת מרכזי בית חינוך</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>גיאוגרפיה
+ ח גלית</t>
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>מגמת יזמות
+ במקביל: מאמי (אומנות בתנועה) · יעל (תזונה) · תמיר (ליווי כדורעף)</t>
         </is>
       </c>
       <c r="I61" s="3" t="n"/>
@@ -7327,29 +7292,28 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>א אנה</t>
-        </is>
-      </c>
+      <c r="D62" s="3" t="n"/>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
+          <t>היסטוריה
+ ז נעמי</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>◦ ישיבת מרכזי בית חינוך</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>היסטוריה
+ ז אלי</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>מגמת יזמות
+ במקביל: מאמי (אומנות בתנועה) · יעל (תזונה) · תמיר (ליווי כדורעף)</t>
         </is>
       </c>
       <c r="I62" s="3" t="n"/>
@@ -7363,27 +7327,27 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>תנ"ך
+ ז אלי</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>היסטוריה
+ ז אלי</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>א אנה</t>
-        </is>
-      </c>
+          <t>חינוך
+ ז אלי / ◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n"/>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>חינוך
+ ז אלי</t>
         </is>
       </c>
       <c r="I63" s="3" t="n"/>
@@ -7402,17 +7366,18 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>תנ"ך
+ ז אלי</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>◦ מפגשה (מעגלי שיח)</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>◦ ישיבת צוות חטיבה</t>
         </is>
       </c>
       <c r="H64" s="3" t="n"/>
@@ -7430,7 +7395,12 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E65" s="3" t="n"/>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>היסטוריה
+ ז אלי</t>
+        </is>
+      </c>
       <c r="F65" s="3" t="n"/>
       <c r="G65" s="3" t="n"/>
       <c r="H65" s="3" t="n"/>
@@ -7439,7 +7409,7 @@
     <row r="67">
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה אסיף בניש</t>
+          <t>מערכת שעות למורה אנה זטרברג</t>
         </is>
       </c>
     </row>
@@ -7502,27 +7472,28 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>שפה
- ט תמיר</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>שפה
- ט תמיר</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>מגמת חדשנות וטכנולוגיה
- במקביל: חסן (ליווי מגמה ימית) · רובי (אומנויות) · שרית (בישול וספורט אתגרי)</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="n"/>
+          <t>עם צופיה
+ א אנה</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>א אנה</t>
+        </is>
+      </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>מגמת יזמות
- במקביל: מאמי (אומנות בתנועה) · חסן (ספורט) · תמיר (ימאות)</t>
+          <t>ג דליה</t>
         </is>
       </c>
       <c r="I70" s="3" t="n"/>
@@ -7536,31 +7507,28 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>חינוך פיננסי
- ט תמיר</t>
+          <t>◦ הדרכת שפה (קטיה)</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>שפה
- ט תמיר</t>
+          <t>א פנינה</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>מגמת חדשנות וטכנולוגיה
- במקביל: חסן (ליווי מגמה ימית) · רובי (אומנויות) · שרית (בישול וספורט אתגרי)</t>
+          <t>עם צופיה
+ א אנה</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>◦ הדרכת שפה חט"ב (זוהר)</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>מגמת יזמות
- במקביל: מאמי (אומנות בתנועה) · חסן (ספורט) · תמיר (ימאות)</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="I71" s="3" t="n"/>
@@ -7574,8 +7542,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>מדעים
- ז אלי</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -7585,14 +7552,17 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>◦ ישיבת מרכזי בית חינוך</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="n"/>
+          <t>א אנה</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>א אנה</t>
+        </is>
+      </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>מדעים
- ז נעמי</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="I72" s="3" t="n"/>
@@ -7606,8 +7576,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>מדעים
- ז אלי</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -7617,19 +7586,17 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>◦ ישיבת מרכזי בית חינוך</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>שפה
- ט אסיף</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>מדעים
- ז נעמי</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="I73" s="3" t="n"/>
@@ -7643,32 +7610,27 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>חינוך פיננסי
- ט אסיף</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>שפה
- ט אסיף</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>חינוך
- ט אסיף</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>שפה
- ט אסיף</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>חינוך
- ט אסיף</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="I74" s="3" t="n"/>
@@ -7685,16 +7647,19 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E75" s="3" t="n"/>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>א אנה</t>
+        </is>
+      </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>חינוך
- ט אסיף</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>◦ ישיבת צוות חטיבה</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="H75" s="3" t="n"/>
@@ -7721,7 +7686,7 @@
     <row r="78">
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה ארז</t>
+          <t>מערכת שעות למורה אסיף בניש</t>
         </is>
       </c>
     </row>
@@ -7782,19 +7747,29 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D81" s="3" t="n"/>
-      <c r="E81" s="3" t="n"/>
-      <c r="F81" s="3" t="n"/>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>אנגלית
- ז נעמי</t>
-        </is>
-      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>שפה
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>שפה
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>מגמת חדשנות וטכנולוגיה
+ במקביל: חסן (ליווי מגמה ימית) · רובי (אומנויות) · שרית (בישול וספורט אתגרי)</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n"/>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>אנגלית
- ז נעמי</t>
+          <t>מגמת יזמות
+ במקביל: מאמי (אומנות בתנועה) · חסן (ספורט) · תמיר (ימאות)</t>
         </is>
       </c>
       <c r="I81" s="3" t="n"/>
@@ -7806,19 +7781,33 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D82" s="3" t="n"/>
-      <c r="E82" s="3" t="n"/>
-      <c r="F82" s="3" t="n"/>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>חינוך פיננסי
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>שפה
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>מגמת חדשנות וטכנולוגיה
+ במקביל: חסן (ליווי מגמה ימית) · רובי (אומנויות) · שרית (בישול וספורט אתגרי)</t>
+        </is>
+      </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>אנגלית
- ז אלי</t>
+          <t>◦ הדרכת שפה חט"ב (זוהר)</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>אנגלית
- ז נעמי</t>
+          <t>מגמת יזמות
+ במקביל: מאמי (אומנות בתנועה) · חסן (ספורט) · תמיר (ימאות)</t>
         </is>
       </c>
       <c r="I82" s="3" t="n"/>
@@ -7830,19 +7819,27 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D83" s="3" t="n"/>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>אנגלית
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>מדעים
  ז אלי</t>
         </is>
       </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>◦ ישיבת מרכזי בית חינוך</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n"/>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>אנגלית
- ז אלי</t>
+          <t>מדעים
+ ז נעמי</t>
         </is>
       </c>
       <c r="I83" s="3" t="n"/>
@@ -7854,19 +7851,32 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D84" s="3" t="n"/>
-      <c r="E84" s="3" t="n"/>
-      <c r="F84" s="3" t="n"/>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>מדעים
+ ז אלי</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>◦ ישיבת מרכזי בית חינוך</t>
+        </is>
+      </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>אנגלית
+          <t>שפה
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>מדעים
  ז נעמי</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>אנגלית
- ז אלי</t>
         </is>
       </c>
       <c r="I84" s="3" t="n"/>
@@ -7880,13 +7890,34 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>◦ הדרכת אנגלית (סיגל)</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n"/>
-      <c r="F85" s="3" t="n"/>
-      <c r="G85" s="3" t="n"/>
-      <c r="H85" s="3" t="n"/>
+          <t>חינוך פיננסי
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>שפה
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>חינוך
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>שפה
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>חינוך
+ ט אסיף</t>
+        </is>
+      </c>
       <c r="I85" s="3" t="n"/>
     </row>
     <row r="86">
@@ -7902,8 +7933,17 @@
         </is>
       </c>
       <c r="E86" s="3" t="n"/>
-      <c r="F86" s="3" t="n"/>
-      <c r="G86" s="3" t="n"/>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>חינוך
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>◦ ישיבת צוות חטיבה</t>
+        </is>
+      </c>
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="3" t="n"/>
     </row>
@@ -7928,7 +7968,7 @@
     <row r="89">
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה גלית בצלאל</t>
+          <t>מערכת שעות למורה ארז</t>
         </is>
       </c>
     </row>
@@ -7989,32 +8029,22 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D92" s="3" t="n"/>
+      <c r="E92" s="3" t="n"/>
+      <c r="F92" s="3" t="n"/>
+      <c r="G92" s="3" t="inlineStr">
         <is>
           <t>אנגלית
- ט אסיף</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="n"/>
-      <c r="F92" s="3" t="inlineStr">
+ ז נעמי</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
         <is>
           <t>אנגלית
- ט אסיף</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>אנגלית
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t>חינוך
- ח גלית</t>
-        </is>
-      </c>
+ ז נעמי</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="n"/>
     </row>
     <row r="93">
       <c r="C93" s="2" t="inlineStr">
@@ -8023,32 +8053,22 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D93" s="3" t="n"/>
+      <c r="E93" s="3" t="n"/>
+      <c r="F93" s="3" t="n"/>
+      <c r="G93" s="3" t="inlineStr">
         <is>
           <t>אנגלית
- ט אסיף</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="inlineStr">
+ ז אלי</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
         <is>
           <t>אנגלית
- ט אסיף</t>
-        </is>
-      </c>
-      <c r="G93" s="3" t="inlineStr">
-        <is>
-          <t>אנגלית
- ט אסיף</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="n"/>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>שירה בציבור
- ח גלית</t>
-        </is>
-      </c>
+ ז נעמי</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="n"/>
     </row>
     <row r="94">
       <c r="C94" s="2" t="inlineStr">
@@ -8057,32 +8077,22 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D94" s="3" t="n"/>
+      <c r="E94" s="3" t="n"/>
+      <c r="F94" s="3" t="n"/>
+      <c r="G94" s="3" t="inlineStr">
         <is>
           <t>אנגלית
- ח גלית</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="n"/>
-      <c r="F94" s="3" t="inlineStr">
+ ז אלי</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
         <is>
           <t>אנגלית
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t>אנגלית (עם ארז)
  ז אלי</t>
         </is>
       </c>
-      <c r="H94" s="3" t="n"/>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t>אנגלית
- ח גלית</t>
-        </is>
-      </c>
+      <c r="I94" s="3" t="n"/>
     </row>
     <row r="95">
       <c r="C95" s="2" t="inlineStr">
@@ -8091,37 +8101,22 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="D95" s="3" t="n"/>
+      <c r="E95" s="3" t="n"/>
+      <c r="F95" s="3" t="n"/>
+      <c r="G95" s="3" t="inlineStr">
         <is>
           <t>אנגלית
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="n"/>
-      <c r="F95" s="3" t="inlineStr">
+ ז נעמי</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
         <is>
           <t>אנגלית
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t>אנגלית (עם ארז)
- ז נעמי</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>חינוך
- ח גלית</t>
-        </is>
-      </c>
-      <c r="I95" s="3" t="inlineStr">
-        <is>
-          <t>אנגלית
- ח גלית</t>
-        </is>
-      </c>
+ ז אלי</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="n"/>
     </row>
     <row r="96">
       <c r="C96" s="2" t="inlineStr">
@@ -8136,23 +8131,9 @@
         </is>
       </c>
       <c r="E96" s="3" t="n"/>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>חינוך
- ח גלית</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>אנגלית
- ח גלית</t>
-        </is>
-      </c>
+      <c r="F96" s="3" t="n"/>
+      <c r="G96" s="3" t="n"/>
+      <c r="H96" s="3" t="n"/>
       <c r="I96" s="3" t="n"/>
     </row>
     <row r="97">
@@ -8168,16 +8149,8 @@
         </is>
       </c>
       <c r="E97" s="3" t="n"/>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>◦ ישיבת צוות חטיבה</t>
-        </is>
-      </c>
+      <c r="F97" s="3" t="n"/>
+      <c r="G97" s="3" t="n"/>
       <c r="H97" s="3" t="n"/>
       <c r="I97" s="3" t="n"/>
     </row>
@@ -8195,19 +8168,14 @@
       </c>
       <c r="E98" s="3" t="n"/>
       <c r="F98" s="3" t="n"/>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>אנגלית
- ט תמיר</t>
-        </is>
-      </c>
+      <c r="G98" s="3" t="n"/>
       <c r="H98" s="3" t="n"/>
       <c r="I98" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה דליה מרקוס</t>
+          <t>מערכת שעות למורה גלית בצלאל</t>
         </is>
       </c>
     </row>
@@ -8270,29 +8238,28 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>חצי כיתה עם הילית
- ג דליה</t>
-        </is>
-      </c>
+          <t>אנגלית
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>אנגלית
+ ט אסיף</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>אנגלית
+ ט תמיר</t>
         </is>
       </c>
       <c r="H103" s="3" t="n"/>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>חינוך
+ ח גלית</t>
         </is>
       </c>
     </row>
@@ -8305,28 +8272,28 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
+          <t>אנגלית
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>אנגלית
+ ט אסיף</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>אנגלית
+ ט אסיף</t>
         </is>
       </c>
       <c r="H104" s="3" t="n"/>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>שירה בציבור
+ ח גלית</t>
         </is>
       </c>
     </row>
@@ -8339,24 +8306,28 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="n"/>
+          <t>אנגלית
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n"/>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>אנגלית
+ ט תמיר</t>
+        </is>
+      </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>אנגלית (עם ארז)
+ ז אלי</t>
         </is>
       </c>
       <c r="H105" s="3" t="n"/>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>אנגלית
+ ח גלית</t>
         </is>
       </c>
     </row>
@@ -8369,28 +8340,33 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>◦ הדרכת שפה (קטיה)</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
+          <t>אנגלית
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n"/>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>אנגלית
+ ט תמיר</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="n"/>
+          <t>אנגלית (עם ארז)
+ ז נעמי</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>חינוך
+ ח גלית</t>
+        </is>
+      </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>אנגלית
+ ח גלית</t>
         </is>
       </c>
     </row>
@@ -8403,25 +8379,27 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
+          <t>◦ הדרכת אנגלית (סיגל)</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>◦ מפגשה (מעגלי שיח)</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="n"/>
+          <t>חינוך
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>אנגלית
+ ח גלית</t>
+        </is>
+      </c>
       <c r="I107" s="3" t="n"/>
     </row>
     <row r="108">
@@ -8436,20 +8414,15 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
+      <c r="E108" s="3" t="n"/>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>חצי כיתה עם יפעת
- ג דליה</t>
+          <t>◦ מפגשה (מעגלי שיח)</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>◦ ישיבת צוות חטיבה</t>
         </is>
       </c>
       <c r="H108" s="3" t="n"/>
@@ -8469,14 +8442,19 @@
       </c>
       <c r="E109" s="3" t="n"/>
       <c r="F109" s="3" t="n"/>
-      <c r="G109" s="3" t="n"/>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>אנגלית
+ ט תמיר</t>
+        </is>
+      </c>
       <c r="H109" s="3" t="n"/>
       <c r="I109" s="3" t="n"/>
     </row>
     <row r="111">
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה דני יהב בראון</t>
+          <t>מערכת שעות למורה דליה מרקוס</t>
         </is>
       </c>
     </row>
@@ -8539,28 +8517,29 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
+          <t>ג דניאל</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="n"/>
+          <t>חצי כיתה עם הילית
+ ג דליה</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="n"/>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
+          <t>ג דליה</t>
         </is>
       </c>
     </row>
@@ -8573,28 +8552,28 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
+          <t>ג דניאל</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="n"/>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
+          <t>ג דניאל</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="n"/>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
+          <t>ג דליה</t>
         </is>
       </c>
     </row>
@@ -8607,7 +8586,7 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
+          <t>ג דליה</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -8616,15 +8595,15 @@
         </is>
       </c>
       <c r="F116" s="3" t="n"/>
-      <c r="G116" s="3" t="n"/>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="n"/>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
+          <t>ג דליה</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8616,7 @@
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
+          <t>◦ הדרכת שפה (קטיה)</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
@@ -8645,16 +8624,20 @@
           <t>◦ מפגשה (מעגלי שיח)</t>
         </is>
       </c>
-      <c r="F117" s="3" t="n"/>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
+          <t>ג דניאל</t>
         </is>
       </c>
       <c r="H117" s="3" t="n"/>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
+          <t>ג דליה</t>
         </is>
       </c>
     </row>
@@ -8667,21 +8650,25 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>◦ הדרכת שפה (קטיה)</t>
+          <t>ג דליה</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="n"/>
-      <c r="G118" s="3" t="n"/>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="n"/>
       <c r="I118" s="3" t="n"/>
     </row>
     <row r="119">
@@ -8698,13 +8685,18 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="n"/>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>חצי כיתה עם יפעת
+ ג דליה</t>
+        </is>
+      </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
+          <t>ג דליה</t>
         </is>
       </c>
       <c r="H119" s="3" t="n"/>
@@ -8731,7 +8723,7 @@
     <row r="122">
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה דניאל צאל</t>
+          <t>מערכת שעות למורה דני יהב בראון</t>
         </is>
       </c>
     </row>
@@ -8794,28 +8786,28 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>ו שרית</t>
+          <t>ה דני</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="n"/>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="n"/>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>ה תניה</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>ה דני</t>
         </is>
       </c>
     </row>
@@ -8828,28 +8820,28 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="n"/>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
           <t>ה דני</t>
         </is>
       </c>
-      <c r="E126" s="3" t="inlineStr">
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
         <is>
           <t>ה דני</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="n"/>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="I126" s="3" t="inlineStr">
-        <is>
-          <t>ג דניאל</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8854,7 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>ה תניה</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
@@ -8870,20 +8862,16 @@
           <t>◦ מפגשה (מעגלי שיח)</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+      <c r="F127" s="3" t="n"/>
       <c r="G127" s="3" t="n"/>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>ה דני</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>ה תניה</t>
         </is>
       </c>
     </row>
@@ -8896,7 +8884,7 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>◦ הדרכת שפה (קטיה)</t>
+          <t>ה דני</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -8904,20 +8892,16 @@
           <t>◦ מפגשה (מעגלי שיח)</t>
         </is>
       </c>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
-      <c r="G128" s="3" t="n"/>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
+      <c r="F128" s="3" t="n"/>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="n"/>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>ה דני</t>
         </is>
       </c>
     </row>
@@ -8930,23 +8914,19 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>◦ הדרכת שפה (קטיה)</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="n"/>
       <c r="G129" s="3" t="n"/>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>ה דני</t>
         </is>
       </c>
       <c r="I129" s="3" t="n"/>
@@ -8965,15 +8945,15 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="n"/>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
       <c r="H130" s="3" t="n"/>
       <c r="I130" s="3" t="n"/>
     </row>
@@ -8998,7 +8978,7 @@
     <row r="133">
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה הדר קורצויל</t>
+          <t>מערכת שעות למורה דניאל צאל</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9039,32 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D136" s="3" t="n"/>
-      <c r="E136" s="3" t="n"/>
-      <c r="F136" s="3" t="n"/>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
       <c r="G136" s="3" t="n"/>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>מתמטיקה
- ז אלי</t>
-        </is>
-      </c>
-      <c r="I136" s="3" t="n"/>
+          <t>ג דניאל</t>
+        </is>
+      </c>
+      <c r="I136" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="C137" s="2" t="inlineStr">
@@ -9078,21 +9073,32 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D137" s="3" t="n"/>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>◦ הדרכת מתמטיקה (ויקי)</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="n"/>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
       <c r="G137" s="3" t="n"/>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>מתמטיקה
- ז אלי</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="n"/>
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="C138" s="2" t="inlineStr">
@@ -9101,17 +9107,32 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D138" s="3" t="n"/>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>מתמטיקה
- ז אלי</t>
-        </is>
-      </c>
-      <c r="F138" s="3" t="n"/>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="G138" s="3" t="n"/>
-      <c r="H138" s="3" t="n"/>
-      <c r="I138" s="3" t="n"/>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="C139" s="2" t="inlineStr">
@@ -9120,17 +9141,32 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D139" s="3" t="n"/>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>◦ הדרכת שפה (קטיה)</t>
+        </is>
+      </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>מתמטיקה
- ז אלי</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="n"/>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
       <c r="G139" s="3" t="n"/>
-      <c r="H139" s="3" t="n"/>
-      <c r="I139" s="3" t="n"/>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="C140" s="2" t="inlineStr">
@@ -9139,19 +9175,25 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D140" s="3" t="n"/>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>מתמטיקה
- ז נעמי</t>
-        </is>
-      </c>
-      <c r="F140" s="3" t="n"/>
+          <t>ג דניאל</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="G140" s="3" t="n"/>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>מתמטיקה
- ז נעמי</t>
+          <t>ג דניאל</t>
         </is>
       </c>
       <c r="I140" s="3" t="n"/>
@@ -9170,18 +9212,16 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>מתמטיקה
- ז נעמי</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="n"/>
+          <t>ג דניאל</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
       <c r="G141" s="3" t="n"/>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>מתמטיקה
- ז נעמי</t>
-        </is>
-      </c>
+      <c r="H141" s="3" t="n"/>
       <c r="I141" s="3" t="n"/>
     </row>
     <row r="142">
@@ -9205,7 +9245,7 @@
     <row r="144">
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה הילה</t>
+          <t>מערכת שעות למורה הדר קורצויל</t>
         </is>
       </c>
     </row>
@@ -9267,20 +9307,15 @@
         </is>
       </c>
       <c r="D147" s="3" t="n"/>
-      <c r="E147" s="3" t="inlineStr">
+      <c r="E147" s="3" t="n"/>
+      <c r="F147" s="3" t="n"/>
+      <c r="G147" s="3" t="n"/>
+      <c r="H147" s="3" t="inlineStr">
         <is>
           <t>מתמטיקה
- ח גלית</t>
-        </is>
-      </c>
-      <c r="F147" s="3" t="n"/>
-      <c r="G147" s="3" t="inlineStr">
-        <is>
-          <t>מתמטיקה
- ט אסיף</t>
-        </is>
-      </c>
-      <c r="H147" s="3" t="n"/>
+ ז אלי</t>
+        </is>
+      </c>
       <c r="I147" s="3" t="n"/>
     </row>
     <row r="148">
@@ -9293,18 +9328,17 @@
       <c r="D148" s="3" t="n"/>
       <c r="E148" s="3" t="inlineStr">
         <is>
+          <t>◦ הדרכת מתמטיקה (ויקי)</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="n"/>
+      <c r="G148" s="3" t="n"/>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
           <t>מתמטיקה
- ח גלית</t>
-        </is>
-      </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t>מתמטיקה
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="G148" s="3" t="n"/>
-      <c r="H148" s="3" t="n"/>
+ ז אלי</t>
+        </is>
+      </c>
       <c r="I148" s="3" t="n"/>
     </row>
     <row r="149">
@@ -9318,21 +9352,11 @@
       <c r="E149" s="3" t="inlineStr">
         <is>
           <t>מתמטיקה
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>מתמטיקה
- ט אסיף</t>
-        </is>
-      </c>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>מתמטיקה
- ט תמיר</t>
-        </is>
-      </c>
+ ז אלי</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="n"/>
+      <c r="G149" s="3" t="n"/>
       <c r="H149" s="3" t="n"/>
       <c r="I149" s="3" t="n"/>
     </row>
@@ -9347,15 +9371,10 @@
       <c r="E150" s="3" t="inlineStr">
         <is>
           <t>מתמטיקה
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="inlineStr">
-        <is>
-          <t>מתמטיקה
- ט אסיף</t>
-        </is>
-      </c>
+ ז אלי</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="n"/>
       <c r="G150" s="3" t="n"/>
       <c r="H150" s="3" t="n"/>
       <c r="I150" s="3" t="n"/>
@@ -9370,17 +9389,18 @@
       <c r="D151" s="3" t="n"/>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>◦ הדרכת מתמטיקה (ויקי)</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
           <t>מתמטיקה
- ח גלית</t>
-        </is>
-      </c>
+ ז נעמי</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="n"/>
       <c r="G151" s="3" t="n"/>
-      <c r="H151" s="3" t="n"/>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>מתמטיקה
+ ז נעמי</t>
+        </is>
+      </c>
       <c r="I151" s="3" t="n"/>
     </row>
     <row r="152">
@@ -9395,20 +9415,20 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E152" s="3" t="n"/>
-      <c r="F152" s="3" t="inlineStr">
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>מתמטיקה
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="G152" s="3" t="inlineStr">
+ ז נעמי</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="n"/>
+      <c r="G152" s="3" t="n"/>
+      <c r="H152" s="3" t="inlineStr">
         <is>
           <t>מתמטיקה
- ח גלית</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="n"/>
+ ז נעמי</t>
+        </is>
+      </c>
       <c r="I152" s="3" t="n"/>
     </row>
     <row r="153">
@@ -9423,26 +9443,16 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>מתמטיקה
- ט אסיף</t>
-        </is>
-      </c>
+      <c r="E153" s="3" t="n"/>
       <c r="F153" s="3" t="n"/>
-      <c r="G153" s="3" t="inlineStr">
-        <is>
-          <t>מתמטיקה
- ח גלית</t>
-        </is>
-      </c>
+      <c r="G153" s="3" t="n"/>
       <c r="H153" s="3" t="n"/>
       <c r="I153" s="3" t="n"/>
     </row>
     <row r="155">
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה הילית בן מאיר שטרן</t>
+          <t>מערכת שעות למורה הילה</t>
         </is>
       </c>
     </row>
@@ -9503,25 +9513,20 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>חצי כיתה עם אביטל
- ב אביטל</t>
-        </is>
-      </c>
+      <c r="D158" s="3" t="n"/>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>חצי כיתה עם דליה
- ג דליה</t>
-        </is>
-      </c>
-      <c r="F158" s="3" t="inlineStr">
-        <is>
-          <t>עם יעל
- ה דני</t>
-        </is>
-      </c>
-      <c r="G158" s="3" t="n"/>
+          <t>מתמטיקה
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="n"/>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>מתמטיקה
+ ט אסיף</t>
+        </is>
+      </c>
       <c r="H158" s="3" t="n"/>
       <c r="I158" s="3" t="n"/>
     </row>
@@ -9535,22 +9540,17 @@
       <c r="D159" s="3" t="n"/>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>עם חגית
- א אנה</t>
+          <t>מתמטיקה
+ ח גלית</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>עם יעל
- ה דני</t>
-        </is>
-      </c>
-      <c r="G159" s="3" t="inlineStr">
-        <is>
-          <t>עם יפעת
- ב אביטל</t>
-        </is>
-      </c>
+          <t>מתמטיקה
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="n"/>
       <c r="H159" s="3" t="n"/>
       <c r="I159" s="3" t="n"/>
     </row>
@@ -9561,28 +9561,23 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>עם יפעת
- ב יערה</t>
-        </is>
-      </c>
+      <c r="D160" s="3" t="n"/>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>עם יעל
- ה תניה</t>
+          <t>מתמטיקה
+ ט תמיר</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>עם יפעת
- ג דליה</t>
+          <t>מתמטיקה
+ ט אסיף</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>עם יפעת
- ג דניאל</t>
+          <t>מתמטיקה
+ ט תמיר</t>
         </is>
       </c>
       <c r="H160" s="3" t="n"/>
@@ -9595,19 +9590,19 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>עם יפעת
- ג לייה</t>
-        </is>
-      </c>
+      <c r="D161" s="3" t="n"/>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>עם יעל
- ה תניה</t>
-        </is>
-      </c>
-      <c r="F161" s="3" t="n"/>
+          <t>מתמטיקה
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>מתמטיקה
+ ט אסיף</t>
+        </is>
+      </c>
       <c r="G161" s="3" t="n"/>
       <c r="H161" s="3" t="n"/>
       <c r="I161" s="3" t="n"/>
@@ -9619,25 +9614,19 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>עם יפעת
- ב יערה</t>
-        </is>
-      </c>
+      <c r="D162" s="3" t="n"/>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>עם חגית
- א פנינה</t>
-        </is>
-      </c>
-      <c r="F162" s="3" t="n"/>
-      <c r="G162" s="3" t="inlineStr">
-        <is>
-          <t>עם יפעת
- ג דניאל</t>
-        </is>
-      </c>
+          <t>◦ הדרכת מתמטיקה (ויקי)</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>מתמטיקה
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="n"/>
       <c r="H162" s="3" t="n"/>
       <c r="I162" s="3" t="n"/>
     </row>
@@ -9654,11 +9643,16 @@
         </is>
       </c>
       <c r="E163" s="3" t="n"/>
-      <c r="F163" s="3" t="n"/>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>מתמטיקה
+ ט תמיר</t>
+        </is>
+      </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>עם יפעת
- ג לייה</t>
+          <t>מתמטיקה
+ ח גלית</t>
         </is>
       </c>
       <c r="H163" s="3" t="n"/>
@@ -9676,16 +9670,26 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E164" s="3" t="n"/>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>מתמטיקה
+ ט אסיף</t>
+        </is>
+      </c>
       <c r="F164" s="3" t="n"/>
-      <c r="G164" s="3" t="n"/>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>מתמטיקה
+ ח גלית</t>
+        </is>
+      </c>
       <c r="H164" s="3" t="n"/>
       <c r="I164" s="3" t="n"/>
     </row>
     <row r="166">
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה חגית אבידן</t>
+          <t>מערכת שעות למורה הילית בן מאיר שטרן</t>
         </is>
       </c>
     </row>
@@ -9746,9 +9750,24 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D169" s="3" t="n"/>
-      <c r="E169" s="3" t="n"/>
-      <c r="F169" s="3" t="n"/>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>חצי כיתה עם אביטל
+ ב אביטל</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>חצי כיתה עם דליה
+ ג דליה</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>עם יעל
+ ה דני</t>
+        </is>
+      </c>
       <c r="G169" s="3" t="n"/>
       <c r="H169" s="3" t="n"/>
       <c r="I169" s="3" t="n"/>
@@ -9760,20 +9779,25 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>חצי כיתה עם אינס
- ד אינס</t>
-        </is>
-      </c>
+      <c r="D170" s="3" t="n"/>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>עם הילית
+          <t>עם חגית
  א אנה</t>
         </is>
       </c>
-      <c r="F170" s="3" t="n"/>
-      <c r="G170" s="3" t="n"/>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>עם יעל
+ ה דני</t>
+        </is>
+      </c>
+      <c r="G170" s="3" t="inlineStr">
+        <is>
+          <t>עם יפעת
+ ב אביטל</t>
+        </is>
+      </c>
       <c r="H170" s="3" t="n"/>
       <c r="I170" s="3" t="n"/>
     </row>
@@ -9786,23 +9810,28 @@
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>חצי כיתה עם אינס
- ד אינס</t>
+          <t>עם יפעת
+ ב יערה</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
+          <t>עם יעל
+ ה תניה</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
           <t>עם יפעת
- א אנה</t>
-        </is>
-      </c>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t>מגמת אומנויות
- במקביל: חסן (ליווי מגמה ימית) · יעל (בישול וספורט אתגרי) · אופיר (חדשנות וטכנולוגיה)</t>
-        </is>
-      </c>
-      <c r="G171" s="3" t="n"/>
+ ג דליה</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>עם יפעת
+ ג דניאל</t>
+        </is>
+      </c>
       <c r="H171" s="3" t="n"/>
       <c r="I171" s="3" t="n"/>
     </row>
@@ -9813,19 +9842,19 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D172" s="3" t="n"/>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>עם יפעת
+ ג לייה</t>
+        </is>
+      </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>עם יפעת
- א פנינה</t>
-        </is>
-      </c>
-      <c r="F172" s="3" t="inlineStr">
-        <is>
-          <t>מגמת אומנויות
- במקביל: חסן (ליווי מגמה ימית) · יעל (בישול וספורט אתגרי) · אופיר (חדשנות וטכנולוגיה)</t>
-        </is>
-      </c>
+          <t>עם יעל
+ ה תניה</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="n"/>
       <c r="G172" s="3" t="n"/>
       <c r="H172" s="3" t="n"/>
       <c r="I172" s="3" t="n"/>
@@ -9837,20 +9866,25 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D173" s="3" t="n"/>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>עם יפעת
+ ב יערה</t>
+        </is>
+      </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>עם הילית
+          <t>עם חגית
  א פנינה</t>
         </is>
       </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>עם יעל
- ד מירי</t>
-        </is>
-      </c>
-      <c r="G173" s="3" t="n"/>
+      <c r="F173" s="3" t="n"/>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>עם יפעת
+ ג דניאל</t>
+        </is>
+      </c>
       <c r="H173" s="3" t="n"/>
       <c r="I173" s="3" t="n"/>
     </row>
@@ -9867,13 +9901,13 @@
         </is>
       </c>
       <c r="E174" s="3" t="n"/>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>עם יעל
- ד מירי</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="n"/>
+      <c r="F174" s="3" t="n"/>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>עם יפעת
+ ג לייה</t>
+        </is>
+      </c>
       <c r="H174" s="3" t="n"/>
       <c r="I174" s="3" t="n"/>
     </row>
@@ -9898,7 +9932,7 @@
     <row r="177">
       <c r="C177" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה חסאן סראחן</t>
+          <t>מערכת שעות למורה חגית אבידן</t>
         </is>
       </c>
     </row>
@@ -9961,19 +9995,9 @@
       </c>
       <c r="D180" s="3" t="n"/>
       <c r="E180" s="3" t="n"/>
-      <c r="F180" s="3" t="inlineStr">
-        <is>
-          <t>מגמת ליווי מגמה ימית
- במקביל: רובי (אומנויות) · שרית (בישול וספורט אתגרי) · אסיף (חדשנות וטכנולוגיה)</t>
-        </is>
-      </c>
+      <c r="F180" s="3" t="n"/>
       <c r="G180" s="3" t="n"/>
-      <c r="H180" s="3" t="inlineStr">
-        <is>
-          <t>מגמת ספורט
- במקביל: אסיף (יזמות) · מאמי (אומנות בתנועה) · תמיר (ימאות)</t>
-        </is>
-      </c>
+      <c r="H180" s="3" t="n"/>
       <c r="I180" s="3" t="n"/>
     </row>
     <row r="181">
@@ -9985,29 +10009,19 @@
       </c>
       <c r="D181" s="3" t="inlineStr">
         <is>
-          <t>חינוך גופני
- ז נעמי / חינוך גופני
- ז אלי</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="n"/>
-      <c r="F181" s="3" t="inlineStr">
-        <is>
-          <t>מגמת ליווי מגמה ימית
- במקביל: רובי (אומנויות) · שרית (בישול וספורט אתגרי) · אסיף (חדשנות וטכנולוגיה)</t>
-        </is>
-      </c>
-      <c r="G181" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="H181" s="3" t="inlineStr">
-        <is>
-          <t>מגמת ספורט
- במקביל: אסיף (יזמות) · מאמי (אומנות בתנועה) · תמיר (ימאות)</t>
-        </is>
-      </c>
+          <t>חצי כיתה עם אינס
+ ד אינס</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>עם הילית
+ א אנה</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="n"/>
+      <c r="G181" s="3" t="n"/>
+      <c r="H181" s="3" t="n"/>
       <c r="I181" s="3" t="n"/>
     </row>
     <row r="182">
@@ -10019,32 +10033,24 @@
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>חינוך גופני
- ט תמיר / חינוך גופני
- ט אסיף</t>
+          <t>חצי כיתה עם אינס
+ ד אינס</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>ד מירי</t>
+          <t>עם יפעת
+ א אנה</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>מגמת ליווי מגמה ימית
- במקביל: חגית (אומנויות) · יעל (בישול וספורט אתגרי) · אופיר (חדשנות וטכנולוגיה)</t>
-        </is>
-      </c>
-      <c r="G182" s="3" t="inlineStr">
-        <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="H182" s="3" t="inlineStr">
-        <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
+          <t>מגמת אומנויות
+ במקביל: חסן (ליווי מגמה ימית) · יעל (בישול וספורט אתגרי) · אופיר (חדשנות וטכנולוגיה)</t>
+        </is>
+      </c>
+      <c r="G182" s="3" t="n"/>
+      <c r="H182" s="3" t="n"/>
       <c r="I182" s="3" t="n"/>
     </row>
     <row r="183">
@@ -10054,34 +10060,21 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>חינוך גופני
- ח גלית</t>
-        </is>
-      </c>
+      <c r="D183" s="3" t="n"/>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>ו אורנה</t>
+          <t>עם יפעת
+ א פנינה</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>מגמת ליווי מגמה ימית
- במקביל: חגית (אומנויות) · יעל (בישול וספורט אתגרי) · אופיר (חדשנות וטכנולוגיה)</t>
-        </is>
-      </c>
-      <c r="G183" s="3" t="inlineStr">
-        <is>
-          <t>חינוך גופני
- ח גלית</t>
-        </is>
-      </c>
-      <c r="H183" s="3" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
+          <t>מגמת אומנויות
+ במקביל: חסן (ליווי מגמה ימית) · יעל (בישול וספורט אתגרי) · אופיר (חדשנות וטכנולוגיה)</t>
+        </is>
+      </c>
+      <c r="G183" s="3" t="n"/>
+      <c r="H183" s="3" t="n"/>
       <c r="I183" s="3" t="n"/>
     </row>
     <row r="184">
@@ -10091,29 +10084,21 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="n"/>
+      <c r="D184" s="3" t="n"/>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>עם הילית
+ א פנינה</t>
+        </is>
+      </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="G184" s="3" t="inlineStr">
-        <is>
-          <t>חינוך גופני
- ז נעמי / חינוך גופני
- ז אלי</t>
-        </is>
-      </c>
-      <c r="H184" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
+          <t>עם יעל
+ ד מירי</t>
+        </is>
+      </c>
+      <c r="G184" s="3" t="n"/>
+      <c r="H184" s="3" t="n"/>
       <c r="I184" s="3" t="n"/>
     </row>
     <row r="185">
@@ -10131,16 +10116,11 @@
       <c r="E185" s="3" t="n"/>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="G185" s="3" t="inlineStr">
-        <is>
-          <t>חינוך גופני
- ט תמיר / חינוך גופני
- ט אסיף</t>
-        </is>
-      </c>
+          <t>עם יעל
+ ד מירי</t>
+        </is>
+      </c>
+      <c r="G185" s="3" t="n"/>
       <c r="H185" s="3" t="n"/>
       <c r="I185" s="3" t="n"/>
     </row>
@@ -10165,7 +10145,7 @@
     <row r="188">
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה טלי ברינברג</t>
+          <t>מערכת שעות למורה חסאן סראחן</t>
         </is>
       </c>
     </row>
@@ -10228,9 +10208,19 @@
       </c>
       <c r="D191" s="3" t="n"/>
       <c r="E191" s="3" t="n"/>
-      <c r="F191" s="3" t="n"/>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>מגמת ליווי מגמה ימית
+ במקביל: רובי (אומנויות) · שרית (בישול וספורט אתגרי) · אסיף (חדשנות וטכנולוגיה)</t>
+        </is>
+      </c>
       <c r="G191" s="3" t="n"/>
-      <c r="H191" s="3" t="n"/>
+      <c r="H191" s="3" t="inlineStr">
+        <is>
+          <t>מגמת ספורט
+ במקביל: אסיף (יזמות) · מאמי (אומנות בתנועה) · תמיר (ימאות)</t>
+        </is>
+      </c>
       <c r="I191" s="3" t="n"/>
     </row>
     <row r="192">
@@ -10240,15 +10230,31 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D192" s="3" t="n"/>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="n"/>
-      <c r="G192" s="3" t="n"/>
-      <c r="H192" s="3" t="n"/>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>חינוך גופני
+ ז נעמי / חינוך גופני
+ ז אלי</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="n"/>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>מגמת ליווי מגמה ימית
+ במקביל: רובי (אומנויות) · שרית (בישול וספורט אתגרי) · אסיף (חדשנות וטכנולוגיה)</t>
+        </is>
+      </c>
+      <c r="G192" s="3" t="inlineStr">
+        <is>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="H192" s="3" t="inlineStr">
+        <is>
+          <t>מגמת ספורט
+ במקביל: אסיף (יזמות) · מאמי (אומנות בתנועה) · תמיר (ימאות)</t>
+        </is>
+      </c>
       <c r="I192" s="3" t="n"/>
     </row>
     <row r="193">
@@ -10258,19 +10264,34 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D193" s="3" t="n"/>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>חינוך גופני
+ ט תמיר / חינוך גופני
+ ט אסיף</t>
+        </is>
+      </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>ב יערה</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="G193" s="3" t="n"/>
-      <c r="H193" s="3" t="n"/>
+          <t>מגמת ליווי מגמה ימית
+ במקביל: חגית (אומנויות) · יעל (בישול וספורט אתגרי) · אופיר (חדשנות וטכנולוגיה)</t>
+        </is>
+      </c>
+      <c r="G193" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="H193" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
       <c r="I193" s="3" t="n"/>
     </row>
     <row r="194">
@@ -10280,19 +10301,34 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D194" s="3" t="n"/>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>חינוך גופני
+ ח גלית</t>
+        </is>
+      </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
+          <t>ו אורנה</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="G194" s="3" t="n"/>
-      <c r="H194" s="3" t="n"/>
+          <t>מגמת ליווי מגמה ימית
+ במקביל: חגית (אומנויות) · יעל (בישול וספורט אתגרי) · אופיר (חדשנות וטכנולוגיה)</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>חינוך גופני
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="H194" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
       <c r="I194" s="3" t="n"/>
     </row>
     <row r="195">
@@ -10302,15 +10338,29 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D195" s="3" t="n"/>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>ד אינס</t>
+        </is>
+      </c>
       <c r="E195" s="3" t="n"/>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="G195" s="3" t="n"/>
-      <c r="H195" s="3" t="n"/>
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>חינוך גופני
+ ז נעמי / חינוך גופני
+ ז אלי</t>
+        </is>
+      </c>
+      <c r="H195" s="3" t="inlineStr">
+        <is>
+          <t>ו שרית</t>
+        </is>
+      </c>
       <c r="I195" s="3" t="n"/>
     </row>
     <row r="196">
@@ -10325,17 +10375,19 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+      <c r="E196" s="3" t="n"/>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="G196" s="3" t="n"/>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>חינוך גופני
+ ט תמיר / חינוך גופני
+ ט אסיף</t>
+        </is>
+      </c>
       <c r="H196" s="3" t="n"/>
       <c r="I196" s="3" t="n"/>
     </row>
@@ -10360,7 +10412,7 @@
     <row r="199">
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה יעל ליפשיץ</t>
+          <t>מערכת שעות למורה טלי ברינברג</t>
         </is>
       </c>
     </row>
@@ -10422,25 +10474,10 @@
         </is>
       </c>
       <c r="D202" s="3" t="n"/>
-      <c r="E202" s="3" t="inlineStr">
-        <is>
-          <t>עם יפעת
- ו שרית</t>
-        </is>
-      </c>
-      <c r="F202" s="3" t="inlineStr">
-        <is>
-          <t>עם הילית
- ה דני</t>
-        </is>
-      </c>
+      <c r="E202" s="3" t="n"/>
+      <c r="F202" s="3" t="n"/>
       <c r="G202" s="3" t="n"/>
-      <c r="H202" s="3" t="inlineStr">
-        <is>
-          <t>חצי כיתה עם אינס
- ד אינס</t>
-        </is>
-      </c>
+      <c r="H202" s="3" t="n"/>
       <c r="I202" s="3" t="n"/>
     </row>
     <row r="203">
@@ -10453,23 +10490,12 @@
       <c r="D203" s="3" t="n"/>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>עם יפעת
- ו שרית</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>עם הילית
- ה דני</t>
-        </is>
-      </c>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="n"/>
       <c r="G203" s="3" t="n"/>
-      <c r="H203" s="3" t="inlineStr">
-        <is>
-          <t>חצי כיתה עם אינס
- ד אינס</t>
-        </is>
-      </c>
+      <c r="H203" s="3" t="n"/>
       <c r="I203" s="3" t="n"/>
     </row>
     <row r="204">
@@ -10482,23 +10508,16 @@
       <c r="D204" s="3" t="n"/>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>עם הילית
- ה תניה</t>
+          <t>ב יערה</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>מגמת בישול וספורט אתגרי
- במקביל: חסן (ליווי מגמה ימית) · חגית (אומנויות) · אופיר (חדשנות וטכנולוגיה)</t>
+          <t>ב יערה</t>
         </is>
       </c>
       <c r="G204" s="3" t="n"/>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>מגמת תזונה
- במקביל: אלי (יזמות) · מאמי (אומנות בתנועה) · תמיר (ליווי כדורעף)</t>
-        </is>
-      </c>
+      <c r="H204" s="3" t="n"/>
       <c r="I204" s="3" t="n"/>
     </row>
     <row r="205">
@@ -10511,23 +10530,16 @@
       <c r="D205" s="3" t="n"/>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>עם הילית
- ה תניה</t>
+          <t>ב אביטל</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>מגמת בישול וספורט אתגרי
- במקביל: חסן (ליווי מגמה ימית) · חגית (אומנויות) · אופיר (חדשנות וטכנולוגיה)</t>
+          <t>ב אביטל</t>
         </is>
       </c>
       <c r="G205" s="3" t="n"/>
-      <c r="H205" s="3" t="inlineStr">
-        <is>
-          <t>מגמת תזונה
- במקביל: אלי (יזמות) · מאמי (אומנות בתנועה) · תמיר (ליווי כדורעף)</t>
-        </is>
-      </c>
+      <c r="H205" s="3" t="n"/>
       <c r="I205" s="3" t="n"/>
     </row>
     <row r="206">
@@ -10538,16 +10550,10 @@
         </is>
       </c>
       <c r="D206" s="3" t="n"/>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>עם יפעת
- ו אורנה</t>
-        </is>
-      </c>
+      <c r="E206" s="3" t="n"/>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>עם חגית
- ד מירי</t>
+          <t>ב אביטל</t>
         </is>
       </c>
       <c r="G206" s="3" t="n"/>
@@ -10568,14 +10574,12 @@
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>עם יפעת
- ו אורנה</t>
+          <t>ב יערה</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>עם חגית
- ד מירי</t>
+          <t>ב יערה</t>
         </is>
       </c>
       <c r="G207" s="3" t="n"/>
@@ -10603,7 +10607,7 @@
     <row r="210">
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה יערה שיכט</t>
+          <t>מערכת שעות למורה יעל ליפשיץ</t>
         </is>
       </c>
     </row>
@@ -10664,32 +10668,27 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D213" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="E213" s="3" t="n"/>
+      <c r="D213" s="3" t="n"/>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>עם יפעת
+ ו שרית</t>
+        </is>
+      </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="G213" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+          <t>עם הילית
+ ה דני</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="n"/>
       <c r="H213" s="3" t="inlineStr">
         <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="I213" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+          <t>חצי כיתה עם אינס
+ ד אינס</t>
+        </is>
+      </c>
+      <c r="I213" s="3" t="n"/>
     </row>
     <row r="214">
       <c r="C214" s="2" t="inlineStr">
@@ -10698,32 +10697,27 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D214" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="E214" s="3" t="n"/>
+      <c r="D214" s="3" t="n"/>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>עם יפעת
+ ו שרית</t>
+        </is>
+      </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="G214" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+          <t>עם הילית
+ ה דני</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="n"/>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="I214" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+          <t>חצי כיתה עם אינס
+ ד אינס</t>
+        </is>
+      </c>
+      <c r="I214" s="3" t="n"/>
     </row>
     <row r="215">
       <c r="C215" s="2" t="inlineStr">
@@ -10732,32 +10726,27 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D215" s="3" t="inlineStr">
-        <is>
-          <t>◦ הדרכת שפה (קטיה)</t>
-        </is>
-      </c>
-      <c r="E215" s="3" t="n"/>
+      <c r="D215" s="3" t="n"/>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>עם הילית
+ ה תניה</t>
+        </is>
+      </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>◦ ישיבת מרכזי בית חינוך</t>
-        </is>
-      </c>
-      <c r="G215" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+          <t>מגמת בישול וספורט אתגרי
+ במקביל: חסן (ליווי מגמה ימית) · חגית (אומנויות) · אופיר (חדשנות וטכנולוגיה)</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="n"/>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
-      <c r="I215" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+          <t>מגמת תזונה
+ במקביל: אלי (יזמות) · מאמי (אומנות בתנועה) · תמיר (ליווי כדורעף)</t>
+        </is>
+      </c>
+      <c r="I215" s="3" t="n"/>
     </row>
     <row r="216">
       <c r="C216" s="2" t="inlineStr">
@@ -10766,32 +10755,27 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D216" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="E216" s="3" t="n"/>
+      <c r="D216" s="3" t="n"/>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>עם הילית
+ ה תניה</t>
+        </is>
+      </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>◦ ישיבת מרכזי בית חינוך</t>
-        </is>
-      </c>
-      <c r="G216" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
+          <t>מגמת בישול וספורט אתגרי
+ במקביל: חסן (ליווי מגמה ימית) · חגית (אומנויות) · אופיר (חדשנות וטכנולוגיה)</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="n"/>
       <c r="H216" s="3" t="inlineStr">
         <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="I216" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+          <t>מגמת תזונה
+ במקביל: אלי (יזמות) · מאמי (אומנות בתנועה) · תמיר (ליווי כדורעף)</t>
+        </is>
+      </c>
+      <c r="I216" s="3" t="n"/>
     </row>
     <row r="217">
       <c r="C217" s="2" t="inlineStr">
@@ -10800,27 +10784,21 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D217" s="3" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="n"/>
+      <c r="D217" s="3" t="n"/>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>עם יפעת
+ ו אורנה</t>
+        </is>
+      </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="G217" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="H217" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+          <t>עם חגית
+ ד מירי</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="n"/>
+      <c r="H217" s="3" t="n"/>
       <c r="I217" s="3" t="n"/>
     </row>
     <row r="218">
@@ -10835,17 +10813,19 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E218" s="3" t="n"/>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>עם יפעת
+ ו אורנה</t>
+        </is>
+      </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="G218" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
+          <t>עם חגית
+ ד מירי</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="n"/>
       <c r="H218" s="3" t="n"/>
       <c r="I218" s="3" t="n"/>
     </row>
@@ -10870,7 +10850,7 @@
     <row r="221">
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה יפעת גולדבלט</t>
+          <t>מערכת שעות למורה יערה שיכט</t>
         </is>
       </c>
     </row>
@@ -10931,17 +10911,32 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D224" s="3" t="n"/>
-      <c r="E224" s="3" t="inlineStr">
-        <is>
-          <t>עם יעל
- ו שרית</t>
-        </is>
-      </c>
-      <c r="F224" s="3" t="n"/>
-      <c r="G224" s="3" t="n"/>
-      <c r="H224" s="3" t="n"/>
-      <c r="I224" s="3" t="n"/>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="n"/>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="I224" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="C225" s="2" t="inlineStr">
@@ -10950,27 +10945,32 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D225" s="3" t="n"/>
-      <c r="E225" s="3" t="inlineStr">
-        <is>
-          <t>עם יעל
- ו שרית</t>
-        </is>
-      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="n"/>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>חצי כיתה עם אביטל
- ב אביטל</t>
+          <t>ב יערה</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>עם הילית
- ב אביטל</t>
-        </is>
-      </c>
-      <c r="H225" s="3" t="n"/>
-      <c r="I225" s="3" t="n"/>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="I225" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="C226" s="2" t="inlineStr">
@@ -10981,30 +10981,30 @@
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>עם הילית
- ב יערה</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="inlineStr">
-        <is>
-          <t>עם חגית
- א אנה</t>
-        </is>
-      </c>
+          <t>◦ הדרכת שפה (קטיה)</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="n"/>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>עם הילית
- ג דליה</t>
+          <t>◦ ישיבת מרכזי בית חינוך</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>עם הילית
- ג דניאל</t>
-        </is>
-      </c>
-      <c r="H226" s="3" t="n"/>
-      <c r="I226" s="3" t="n"/>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="I226" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="C227" s="2" t="inlineStr">
@@ -11015,20 +11015,30 @@
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>עם הילית
- ג לייה</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>עם חגית
- א פנינה</t>
-        </is>
-      </c>
-      <c r="F227" s="3" t="n"/>
-      <c r="G227" s="3" t="n"/>
-      <c r="H227" s="3" t="n"/>
-      <c r="I227" s="3" t="n"/>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="n"/>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>◦ ישיבת מרכזי בית חינוך</t>
+        </is>
+      </c>
+      <c r="G227" s="3" t="inlineStr">
+        <is>
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="H227" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="I227" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="C228" s="2" t="inlineStr">
@@ -11039,24 +11049,25 @@
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>עם הילית
- ב יערה</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>עם יעל
- ו אורנה</t>
-        </is>
-      </c>
-      <c r="F228" s="3" t="n"/>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="n"/>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>עם הילית
- ג דניאל</t>
-        </is>
-      </c>
-      <c r="H228" s="3" t="n"/>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="H228" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
       <c r="I228" s="3" t="n"/>
     </row>
     <row r="229">
@@ -11071,22 +11082,15 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E229" s="3" t="inlineStr">
-        <is>
-          <t>עם יעל
- ו אורנה</t>
-        </is>
-      </c>
+      <c r="E229" s="3" t="n"/>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>חצי כיתה עם דליה
- ג דליה</t>
+          <t>◦ מפגשה (מעגלי שיח)</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>עם הילית
- ג לייה</t>
+          <t>ב יערה</t>
         </is>
       </c>
       <c r="H229" s="3" t="n"/>
@@ -11113,7 +11117,7 @@
     <row r="232">
       <c r="C232" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה לי-אור שפירא</t>
+          <t>מערכת שעות למורה יפעת גולדבלט</t>
         </is>
       </c>
     </row>
@@ -11175,14 +11179,15 @@
         </is>
       </c>
       <c r="D235" s="3" t="n"/>
-      <c r="E235" s="3" t="n"/>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>עם יעל
+ ו שרית</t>
+        </is>
+      </c>
       <c r="F235" s="3" t="n"/>
       <c r="G235" s="3" t="n"/>
-      <c r="H235" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
+      <c r="H235" s="3" t="n"/>
       <c r="I235" s="3" t="n"/>
     </row>
     <row r="236">
@@ -11193,14 +11198,25 @@
         </is>
       </c>
       <c r="D236" s="3" t="n"/>
-      <c r="E236" s="3" t="n"/>
-      <c r="F236" s="3" t="n"/>
-      <c r="G236" s="3" t="n"/>
-      <c r="H236" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>עם יעל
+ ו שרית</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>חצי כיתה עם אביטל
+ ב אביטל</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>עם הילית
+ ב אביטל</t>
+        </is>
+      </c>
+      <c r="H236" s="3" t="n"/>
       <c r="I236" s="3" t="n"/>
     </row>
     <row r="237">
@@ -11210,23 +11226,31 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D237" s="3" t="n"/>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>עם הילית
+ ב יערה</t>
+        </is>
+      </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>עם חגית
+ א אנה</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="G237" s="3" t="n"/>
-      <c r="H237" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
+          <t>עם הילית
+ ג דליה</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr">
+        <is>
+          <t>עם הילית
+ ג דניאל</t>
+        </is>
+      </c>
+      <c r="H237" s="3" t="n"/>
       <c r="I237" s="3" t="n"/>
     </row>
     <row r="238">
@@ -11236,23 +11260,21 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D238" s="3" t="n"/>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>עם הילית
+ ג לייה</t>
+        </is>
+      </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="F238" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
+          <t>עם חגית
+ א פנינה</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="n"/>
       <c r="G238" s="3" t="n"/>
-      <c r="H238" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
+      <c r="H238" s="3" t="n"/>
       <c r="I238" s="3" t="n"/>
     </row>
     <row r="239">
@@ -11262,14 +11284,25 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D239" s="3" t="n"/>
-      <c r="E239" s="3" t="n"/>
-      <c r="F239" s="3" t="inlineStr">
-        <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="G239" s="3" t="n"/>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>עם הילית
+ ב יערה</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>עם יעל
+ ו אורנה</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="n"/>
+      <c r="G239" s="3" t="inlineStr">
+        <is>
+          <t>עם הילית
+ ג דניאל</t>
+        </is>
+      </c>
       <c r="H239" s="3" t="n"/>
       <c r="I239" s="3" t="n"/>
     </row>
@@ -11285,13 +11318,24 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E240" s="3" t="n"/>
+      <c r="E240" s="3" t="inlineStr">
+        <is>
+          <t>עם יעל
+ ו אורנה</t>
+        </is>
+      </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="G240" s="3" t="n"/>
+          <t>חצי כיתה עם דליה
+ ג דליה</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr">
+        <is>
+          <t>עם הילית
+ ג לייה</t>
+        </is>
+      </c>
       <c r="H240" s="3" t="n"/>
       <c r="I240" s="3" t="n"/>
     </row>
@@ -11316,7 +11360,7 @@
     <row r="243">
       <c r="C243" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה לייה גור</t>
+          <t>מערכת שעות למורה לי-אור שפירא</t>
         </is>
       </c>
     </row>
@@ -11377,32 +11421,16 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D246" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+      <c r="D246" s="3" t="n"/>
+      <c r="E246" s="3" t="n"/>
+      <c r="F246" s="3" t="n"/>
       <c r="G246" s="3" t="n"/>
       <c r="H246" s="3" t="inlineStr">
         <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="I246" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+          <t>ד מירי</t>
+        </is>
+      </c>
+      <c r="I246" s="3" t="n"/>
     </row>
     <row r="247">
       <c r="C247" s="2" t="inlineStr">
@@ -11411,32 +11439,16 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D247" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="E247" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="F247" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+      <c r="D247" s="3" t="n"/>
+      <c r="E247" s="3" t="n"/>
+      <c r="F247" s="3" t="n"/>
       <c r="G247" s="3" t="n"/>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="I247" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+          <t>ד מירי</t>
+        </is>
+      </c>
+      <c r="I247" s="3" t="n"/>
     </row>
     <row r="248">
       <c r="C248" s="2" t="inlineStr">
@@ -11445,33 +11457,24 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D248" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+      <c r="D248" s="3" t="n"/>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך
- ח גלית</t>
+          <t>ג דניאל</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>◦ ישיבת מרכזי בית חינוך</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="G248" s="3" t="n"/>
       <c r="H248" s="3" t="inlineStr">
         <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="I248" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+          <t>ד מירי</t>
+        </is>
+      </c>
+      <c r="I248" s="3" t="n"/>
     </row>
     <row r="249">
       <c r="C249" s="2" t="inlineStr">
@@ -11480,33 +11483,24 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D249" s="3" t="inlineStr">
-        <is>
-          <t>◦ הדרכת שפה (קטיה)</t>
-        </is>
-      </c>
+      <c r="D249" s="3" t="n"/>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך
- ח גלית</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>◦ ישיבת מרכזי בית חינוך</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="G249" s="3" t="n"/>
       <c r="H249" s="3" t="inlineStr">
         <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="I249" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+          <t>ד אינס</t>
+        </is>
+      </c>
+      <c r="I249" s="3" t="n"/>
     </row>
     <row r="250">
       <c r="C250" s="2" t="inlineStr">
@@ -11515,27 +11509,15 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D250" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+      <c r="D250" s="3" t="n"/>
+      <c r="E250" s="3" t="n"/>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
+          <t>ה תניה</t>
         </is>
       </c>
       <c r="G250" s="3" t="n"/>
-      <c r="H250" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+      <c r="H250" s="3" t="n"/>
       <c r="I250" s="3" t="n"/>
     </row>
     <row r="251">
@@ -11550,14 +11532,10 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E251" s="3" t="inlineStr">
+      <c r="E251" s="3" t="n"/>
+      <c r="F251" s="3" t="inlineStr">
         <is>
           <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="F251" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
         </is>
       </c>
       <c r="G251" s="3" t="n"/>
@@ -11585,7 +11563,7 @@
     <row r="254">
       <c r="C254" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה מאמי שימאזאקי</t>
+          <t>מערכת שעות למורה לייה גור</t>
         </is>
       </c>
     </row>
@@ -11646,17 +11624,32 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D257" s="3" t="n"/>
-      <c r="E257" s="3" t="n"/>
-      <c r="F257" s="3" t="n"/>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="G257" s="3" t="n"/>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>מגמת אומנות בתנועה
- במקביל: אסיף (יזמות) · חסן (ספורט) · תמיר (ימאות)</t>
-        </is>
-      </c>
-      <c r="I257" s="3" t="n"/>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="I257" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="C258" s="2" t="inlineStr">
@@ -11665,17 +11658,32 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D258" s="3" t="n"/>
-      <c r="E258" s="3" t="n"/>
-      <c r="F258" s="3" t="n"/>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="G258" s="3" t="n"/>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>מגמת אומנות בתנועה
- במקביל: אסיף (יזמות) · חסן (ספורט) · תמיר (ימאות)</t>
-        </is>
-      </c>
-      <c r="I258" s="3" t="n"/>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="I258" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="C259" s="2" t="inlineStr">
@@ -11684,17 +11692,33 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D259" s="3" t="n"/>
-      <c r="E259" s="3" t="n"/>
-      <c r="F259" s="3" t="n"/>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>◦ ישיבת מרכזי בית חינוך</t>
+        </is>
+      </c>
       <c r="G259" s="3" t="n"/>
       <c r="H259" s="3" t="inlineStr">
         <is>
-          <t>מגמת אומנות בתנועה
- במקביל: אלי (יזמות) · יעל (תזונה) · תמיר (ליווי כדורעף)</t>
-        </is>
-      </c>
-      <c r="I259" s="3" t="n"/>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="I259" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="C260" s="2" t="inlineStr">
@@ -11703,17 +11727,33 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D260" s="3" t="n"/>
-      <c r="E260" s="3" t="n"/>
-      <c r="F260" s="3" t="n"/>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>◦ הדרכת שפה (קטיה)</t>
+        </is>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>◦ ישיבת מרכזי בית חינוך</t>
+        </is>
+      </c>
       <c r="G260" s="3" t="n"/>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>מגמת אומנות בתנועה
- במקביל: אלי (יזמות) · יעל (תזונה) · תמיר (ליווי כדורעף)</t>
-        </is>
-      </c>
-      <c r="I260" s="3" t="n"/>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="I260" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="C261" s="2" t="inlineStr">
@@ -11722,11 +11762,27 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D261" s="3" t="n"/>
-      <c r="E261" s="3" t="n"/>
-      <c r="F261" s="3" t="n"/>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
       <c r="G261" s="3" t="n"/>
-      <c r="H261" s="3" t="n"/>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="I261" s="3" t="n"/>
     </row>
     <row r="262">
@@ -11741,8 +11797,16 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E262" s="3" t="n"/>
-      <c r="F262" s="3" t="n"/>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
       <c r="G262" s="3" t="n"/>
       <c r="H262" s="3" t="n"/>
       <c r="I262" s="3" t="n"/>
@@ -11768,7 +11832,7 @@
     <row r="265">
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה מירי בן עמי קריימר</t>
+          <t>מערכת שעות למורה מאמי שימאזאקי</t>
         </is>
       </c>
     </row>
@@ -11829,28 +11893,17 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D268" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
+      <c r="D268" s="3" t="n"/>
       <c r="E268" s="3" t="n"/>
-      <c r="F268" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="G268" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="H268" s="3" t="n"/>
-      <c r="I268" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
+      <c r="F268" s="3" t="n"/>
+      <c r="G268" s="3" t="n"/>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>מגמת אומנות בתנועה
+ במקביל: אסיף (יזמות) · חסן (ספורט) · תמיר (ימאות)</t>
+        </is>
+      </c>
+      <c r="I268" s="3" t="n"/>
     </row>
     <row r="269">
       <c r="C269" s="2" t="inlineStr">
@@ -11859,32 +11912,17 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D269" s="3" t="inlineStr">
-        <is>
-          <t>א אנה</t>
-        </is>
-      </c>
-      <c r="E269" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="F269" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="G269" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="H269" s="3" t="n"/>
-      <c r="I269" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
+      <c r="D269" s="3" t="n"/>
+      <c r="E269" s="3" t="n"/>
+      <c r="F269" s="3" t="n"/>
+      <c r="G269" s="3" t="n"/>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
+          <t>מגמת אומנות בתנועה
+ במקביל: אסיף (יזמות) · חסן (ספורט) · תמיר (ימאות)</t>
+        </is>
+      </c>
+      <c r="I269" s="3" t="n"/>
     </row>
     <row r="270">
       <c r="C270" s="2" t="inlineStr">
@@ -11893,32 +11931,17 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D270" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="E270" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="F270" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="G270" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="H270" s="3" t="n"/>
-      <c r="I270" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
+      <c r="D270" s="3" t="n"/>
+      <c r="E270" s="3" t="n"/>
+      <c r="F270" s="3" t="n"/>
+      <c r="G270" s="3" t="n"/>
+      <c r="H270" s="3" t="inlineStr">
+        <is>
+          <t>מגמת אומנות בתנועה
+ במקביל: אלי (יזמות) · יעל (תזונה) · תמיר (ליווי כדורעף)</t>
+        </is>
+      </c>
+      <c r="I270" s="3" t="n"/>
     </row>
     <row r="271">
       <c r="C271" s="2" t="inlineStr">
@@ -11927,32 +11950,17 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D271" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="E271" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="F271" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="G271" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="H271" s="3" t="n"/>
-      <c r="I271" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
+      <c r="D271" s="3" t="n"/>
+      <c r="E271" s="3" t="n"/>
+      <c r="F271" s="3" t="n"/>
+      <c r="G271" s="3" t="n"/>
+      <c r="H271" s="3" t="inlineStr">
+        <is>
+          <t>מגמת אומנות בתנועה
+ במקביל: אלי (יזמות) · יעל (תזונה) · תמיר (ליווי כדורעף)</t>
+        </is>
+      </c>
+      <c r="I271" s="3" t="n"/>
     </row>
     <row r="272">
       <c r="C272" s="2" t="inlineStr">
@@ -11961,26 +11969,10 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D272" s="3" t="inlineStr">
-        <is>
-          <t>◦ הדרכת שפה (קטיה)</t>
-        </is>
-      </c>
-      <c r="E272" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="F272" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="G272" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
+      <c r="D272" s="3" t="n"/>
+      <c r="E272" s="3" t="n"/>
+      <c r="F272" s="3" t="n"/>
+      <c r="G272" s="3" t="n"/>
       <c r="H272" s="3" t="n"/>
       <c r="I272" s="3" t="n"/>
     </row>
@@ -11996,21 +11988,9 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E273" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="F273" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="G273" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
+      <c r="E273" s="3" t="n"/>
+      <c r="F273" s="3" t="n"/>
+      <c r="G273" s="3" t="n"/>
       <c r="H273" s="3" t="n"/>
       <c r="I273" s="3" t="n"/>
     </row>
@@ -12035,7 +12015,7 @@
     <row r="276">
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה מרים</t>
+          <t>מערכת שעות למורה מירי בן עמי קריימר</t>
         </is>
       </c>
     </row>
@@ -12098,28 +12078,26 @@
       </c>
       <c r="D279" s="3" t="inlineStr">
         <is>
-          <t>ערבית
- ז אלי</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="E279" s="3" t="n"/>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>ערבית
- ט תמיר</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="H279" s="3" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="I279" s="3" t="n"/>
+          <t>ד אינס</t>
+        </is>
+      </c>
+      <c r="H279" s="3" t="n"/>
+      <c r="I279" s="3" t="inlineStr">
+        <is>
+          <t>ד מירי</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="C280" s="2" t="inlineStr">
@@ -12130,27 +12108,30 @@
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>א אנה</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
-      <c r="F280" s="3" t="n"/>
+          <t>ד מירי</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>ד מירי</t>
+        </is>
+      </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>ערבית
- ח גלית</t>
-        </is>
-      </c>
-      <c r="H280" s="3" t="inlineStr">
-        <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
-      <c r="I280" s="3" t="n"/>
+          <t>ד מירי</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="n"/>
+      <c r="I280" s="3" t="inlineStr">
+        <is>
+          <t>ד מירי</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="C281" s="2" t="inlineStr">
@@ -12159,30 +12140,32 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D281" s="3" t="n"/>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>ד מירי</t>
+        </is>
+      </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>ערבית
- ט אסיף</t>
+          <t>◦ מפגשה (מעגלי שיח)</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>ו שרית</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
-      <c r="H281" s="3" t="inlineStr">
-        <is>
-          <t>ערבית
- ח גלית</t>
-        </is>
-      </c>
-      <c r="I281" s="3" t="n"/>
+          <t>ד אינס</t>
+        </is>
+      </c>
+      <c r="H281" s="3" t="n"/>
+      <c r="I281" s="3" t="inlineStr">
+        <is>
+          <t>ד מירי</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="C282" s="2" t="inlineStr">
@@ -12193,31 +12176,30 @@
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>ד אינס</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>ערבית
- ט אסיף</t>
+          <t>◦ מפגשה (מעגלי שיח)</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="H282" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="I282" s="3" t="n"/>
+          <t>ד מירי</t>
+        </is>
+      </c>
+      <c r="H282" s="3" t="n"/>
+      <c r="I282" s="3" t="inlineStr">
+        <is>
+          <t>ד מירי</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="C283" s="2" t="inlineStr">
@@ -12228,27 +12210,25 @@
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>ערבית
- ז נעמי</t>
-        </is>
-      </c>
-      <c r="E283" s="3" t="n"/>
+          <t>◦ הדרכת שפה (קטיה)</t>
+        </is>
+      </c>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>ד מירי</t>
+        </is>
+      </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>ערבית
- ט תמיר</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="H283" s="3" t="inlineStr">
-        <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
+          <t>ד אינס</t>
+        </is>
+      </c>
+      <c r="H283" s="3" t="n"/>
       <c r="I283" s="3" t="n"/>
     </row>
     <row r="284">
@@ -12263,23 +12243,22 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E284" s="3" t="n"/>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>ד אינס</t>
+        </is>
+      </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="H284" s="3" t="inlineStr">
-        <is>
-          <t>ערבית
- ז אלי</t>
-        </is>
-      </c>
+          <t>ד אינס</t>
+        </is>
+      </c>
+      <c r="H284" s="3" t="n"/>
       <c r="I284" s="3" t="n"/>
     </row>
     <row r="285">
@@ -12297,18 +12276,13 @@
       <c r="E285" s="3" t="n"/>
       <c r="F285" s="3" t="n"/>
       <c r="G285" s="3" t="n"/>
-      <c r="H285" s="3" t="inlineStr">
-        <is>
-          <t>ערבית
- ז נעמי</t>
-        </is>
-      </c>
+      <c r="H285" s="3" t="n"/>
       <c r="I285" s="3" t="n"/>
     </row>
     <row r="287">
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה נעמי קציר</t>
+          <t>מערכת שעות למורה מרים</t>
         </is>
       </c>
     </row>
@@ -12371,30 +12345,28 @@
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>חינוך
- ז נעמי</t>
-        </is>
-      </c>
-      <c r="E290" s="3" t="inlineStr">
-        <is>
-          <t>שפה
+          <t>ערבית
  ז אלי</t>
         </is>
       </c>
-      <c r="F290" s="3" t="n"/>
+      <c r="E290" s="3" t="n"/>
+      <c r="F290" s="3" t="inlineStr">
+        <is>
+          <t>ערבית
+ ט תמיר</t>
+        </is>
+      </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>שפה
- ח גלית</t>
-        </is>
-      </c>
-      <c r="H290" s="3" t="n"/>
-      <c r="I290" s="3" t="inlineStr">
-        <is>
-          <t>שפה
- ז אלי</t>
-        </is>
-      </c>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="I290" s="3" t="n"/>
     </row>
     <row r="291">
       <c r="C291" s="2" t="inlineStr">
@@ -12405,29 +12377,27 @@
       </c>
       <c r="D291" s="3" t="inlineStr">
         <is>
-          <t>ספרות
- ח גלית</t>
+          <t>ג דליה</t>
         </is>
       </c>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>שפה
- ז אלי</t>
+          <t>ג דניאל</t>
         </is>
       </c>
       <c r="F291" s="3" t="n"/>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>◦ הדרכת שפה חט"ב (זוהר)</t>
-        </is>
-      </c>
-      <c r="H291" s="3" t="n"/>
-      <c r="I291" s="3" t="inlineStr">
-        <is>
-          <t>שירה בציבור
- ז נעמי</t>
-        </is>
-      </c>
+          <t>ערבית
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="I291" s="3" t="n"/>
     </row>
     <row r="292">
       <c r="C292" s="2" t="inlineStr">
@@ -12439,23 +12409,27 @@
       <c r="D292" s="3" t="n"/>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="F292" s="3" t="n"/>
+          <t>ערבית
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>ו שרית</t>
+        </is>
+      </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>ספרות
- ז נעמי</t>
-        </is>
-      </c>
-      <c r="H292" s="3" t="n"/>
-      <c r="I292" s="3" t="inlineStr">
-        <is>
-          <t>שפה
- ז נעמי</t>
-        </is>
-      </c>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>ערבית
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="I292" s="3" t="n"/>
     </row>
     <row r="293">
       <c r="C293" s="2" t="inlineStr">
@@ -12466,24 +12440,31 @@
       </c>
       <c r="D293" s="3" t="inlineStr">
         <is>
-          <t>שפה
- ז נעמי</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="F293" s="3" t="n"/>
-      <c r="G293" s="3" t="n"/>
-      <c r="H293" s="3" t="n"/>
-      <c r="I293" s="3" t="inlineStr">
-        <is>
-          <t>שפה
- ז נעמי</t>
-        </is>
-      </c>
+          <t>ערבית
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="H293" s="3" t="inlineStr">
+        <is>
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="I293" s="3" t="n"/>
     </row>
     <row r="294">
       <c r="C294" s="2" t="inlineStr">
@@ -12494,24 +12475,27 @@
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>ספרות
- ח גלית</t>
-        </is>
-      </c>
-      <c r="E294" s="3" t="inlineStr">
-        <is>
-          <t>שפה
- ח גלית</t>
-        </is>
-      </c>
+          <t>ערבית
+ ז נעמי</t>
+        </is>
+      </c>
+      <c r="E294" s="3" t="n"/>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>חינוך
- ז נעמי</t>
-        </is>
-      </c>
-      <c r="G294" s="3" t="n"/>
-      <c r="H294" s="3" t="n"/>
+          <t>ערבית
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="H294" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
       <c r="I294" s="3" t="n"/>
     </row>
     <row r="295">
@@ -12526,19 +12510,23 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E295" s="3" t="inlineStr">
-        <is>
-          <t>שפה
- ח גלית</t>
-        </is>
-      </c>
-      <c r="F295" s="3" t="n"/>
+      <c r="E295" s="3" t="n"/>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>◦ ישיבת צוות חטיבה</t>
-        </is>
-      </c>
-      <c r="H295" s="3" t="n"/>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>ערבית
+ ז אלי</t>
+        </is>
+      </c>
       <c r="I295" s="3" t="n"/>
     </row>
     <row r="296">
@@ -12556,13 +12544,18 @@
       <c r="E296" s="3" t="n"/>
       <c r="F296" s="3" t="n"/>
       <c r="G296" s="3" t="n"/>
-      <c r="H296" s="3" t="n"/>
+      <c r="H296" s="3" t="inlineStr">
+        <is>
+          <t>ערבית
+ ז נעמי</t>
+        </is>
+      </c>
       <c r="I296" s="3" t="n"/>
     </row>
     <row r="298">
       <c r="C298" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה סימה דוד</t>
+          <t>מערכת שעות למורה נעמי קציר</t>
         </is>
       </c>
     </row>
@@ -12625,30 +12618,30 @@
       </c>
       <c r="D301" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
+          <t>חינוך
+ ז נעמי</t>
         </is>
       </c>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="F301" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
+          <t>שפה
+ ז אלי</t>
+        </is>
+      </c>
+      <c r="F301" s="3" t="n"/>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="H301" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="I301" s="3" t="n"/>
+          <t>שפה
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="H301" s="3" t="n"/>
+      <c r="I301" s="3" t="inlineStr">
+        <is>
+          <t>שפה
+ ז אלי</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="C302" s="2" t="inlineStr">
@@ -12659,26 +12652,29 @@
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="E302" s="3" t="n"/>
-      <c r="F302" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
+          <t>ספרות
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>שפה
+ ז אלי</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="n"/>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="H302" s="3" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="I302" s="3" t="n"/>
+          <t>◦ הדרכת שפה חט"ב (זוהר)</t>
+        </is>
+      </c>
+      <c r="H302" s="3" t="n"/>
+      <c r="I302" s="3" t="inlineStr">
+        <is>
+          <t>שירה בציבור
+ ז נעמי</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="C303" s="2" t="inlineStr">
@@ -12687,32 +12683,26 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D303" s="3" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
+      <c r="D303" s="3" t="n"/>
       <c r="E303" s="3" t="inlineStr">
         <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="F303" s="3" t="inlineStr">
-        <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="F303" s="3" t="n"/>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="H303" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="I303" s="3" t="n"/>
+          <t>ספרות
+ ז נעמי</t>
+        </is>
+      </c>
+      <c r="H303" s="3" t="n"/>
+      <c r="I303" s="3" t="inlineStr">
+        <is>
+          <t>שפה
+ ז נעמי</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="C304" s="2" t="inlineStr">
@@ -12721,28 +12711,26 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D304" s="3" t="n"/>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>שפה
+ ז נעמי</t>
+        </is>
+      </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>ד אינס</t>
-        </is>
-      </c>
-      <c r="F304" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="G304" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="H304" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="I304" s="3" t="n"/>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="n"/>
+      <c r="G304" s="3" t="n"/>
+      <c r="H304" s="3" t="n"/>
+      <c r="I304" s="3" t="inlineStr">
+        <is>
+          <t>שפה
+ ז נעמי</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="C305" s="2" t="inlineStr">
@@ -12753,29 +12741,24 @@
       </c>
       <c r="D305" s="3" t="inlineStr">
         <is>
-          <t>◦ הדרכת אנגלית (סיגל)</t>
+          <t>ספרות
+ ח גלית</t>
         </is>
       </c>
       <c r="E305" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
+          <t>שפה
+ ח גלית</t>
         </is>
       </c>
       <c r="F305" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="G305" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="H305" s="3" t="inlineStr">
-        <is>
-          <t>ד מירי</t>
-        </is>
-      </c>
+          <t>חינוך
+ ז נעמי</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="n"/>
+      <c r="H305" s="3" t="n"/>
       <c r="I305" s="3" t="n"/>
     </row>
     <row r="306">
@@ -12790,15 +12773,16 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E306" s="3" t="n"/>
-      <c r="F306" s="3" t="inlineStr">
-        <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>שפה
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="n"/>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>ד מירי</t>
+          <t>◦ ישיבת צוות חטיבה</t>
         </is>
       </c>
       <c r="H306" s="3" t="n"/>
@@ -12825,7 +12809,7 @@
     <row r="309">
       <c r="C309" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה פאני קרוטמן</t>
+          <t>מערכת שעות למורה סימה דוד</t>
         </is>
       </c>
     </row>
@@ -12886,21 +12870,29 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D312" s="3" t="n"/>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
-      <c r="F312" s="3" t="n"/>
+          <t>ד אינס</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="inlineStr">
+        <is>
+          <t>ו שרית</t>
+        </is>
+      </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>ה דני</t>
         </is>
       </c>
       <c r="H312" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>ו שרית</t>
         </is>
       </c>
       <c r="I312" s="3" t="n"/>
@@ -12914,19 +12906,23 @@
       </c>
       <c r="D313" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="E313" s="3" t="n"/>
-      <c r="F313" s="3" t="n"/>
+      <c r="F313" s="3" t="inlineStr">
+        <is>
+          <t>ד אינס</t>
+        </is>
+      </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>ג לייה</t>
+          <t>ה תניה</t>
         </is>
       </c>
       <c r="H313" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>ה דני</t>
         </is>
       </c>
       <c r="I313" s="3" t="n"/>
@@ -12940,19 +12936,27 @@
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
+          <t>ה דני</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
-      <c r="F314" s="3" t="n"/>
-      <c r="G314" s="3" t="n"/>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="G314" s="3" t="inlineStr">
+        <is>
+          <t>ו אורנה</t>
+        </is>
+      </c>
       <c r="H314" s="3" t="inlineStr">
         <is>
-          <t>ב יערה</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="I314" s="3" t="n"/>
@@ -12964,25 +12968,25 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D315" s="3" t="inlineStr">
-        <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
+      <c r="D315" s="3" t="n"/>
       <c r="E315" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
-        </is>
-      </c>
-      <c r="F315" s="3" t="n"/>
+          <t>ד אינס</t>
+        </is>
+      </c>
+      <c r="F315" s="3" t="inlineStr">
+        <is>
+          <t>ו שרית</t>
+        </is>
+      </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>ב יערה</t>
+          <t>ו אורנה</t>
         </is>
       </c>
       <c r="H315" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="I315" s="3" t="n"/>
@@ -12994,17 +12998,29 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D316" s="3" t="n"/>
-      <c r="E316" s="3" t="n"/>
-      <c r="F316" s="3" t="n"/>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>◦ הדרכת אנגלית (סיגל)</t>
+        </is>
+      </c>
+      <c r="E316" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="F316" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="H316" s="3" t="inlineStr">
+        <is>
           <t>ד מירי</t>
-        </is>
-      </c>
-      <c r="H316" s="3" t="inlineStr">
-        <is>
-          <t>ד אינס</t>
         </is>
       </c>
       <c r="I316" s="3" t="n"/>
@@ -13022,10 +13038,14 @@
         </is>
       </c>
       <c r="E317" s="3" t="n"/>
-      <c r="F317" s="3" t="n"/>
+      <c r="F317" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>ב אביטל</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="H317" s="3" t="n"/>
@@ -13052,7 +13072,7 @@
     <row r="320">
       <c r="C320" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה פנינה קרפטי</t>
+          <t>מערכת שעות למורה פאני קרוטמן</t>
         </is>
       </c>
     </row>
@@ -13113,32 +13133,24 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D323" s="3" t="inlineStr">
+      <c r="D323" s="3" t="n"/>
+      <c r="E323" s="3" t="inlineStr">
         <is>
           <t>א פנינה</t>
         </is>
       </c>
-      <c r="E323" s="3" t="n"/>
-      <c r="F323" s="3" t="inlineStr">
-        <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
+      <c r="F323" s="3" t="n"/>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
+          <t>ג דניאל</t>
         </is>
       </c>
       <c r="H323" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
-      <c r="I323" s="3" t="inlineStr">
-        <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
+          <t>א אנה</t>
+        </is>
+      </c>
+      <c r="I323" s="3" t="n"/>
     </row>
     <row r="324">
       <c r="C324" s="2" t="inlineStr">
@@ -13149,30 +13161,22 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>◦ הדרכת שפה (קטיה)</t>
+          <t>א פנינה</t>
         </is>
       </c>
       <c r="E324" s="3" t="n"/>
-      <c r="F324" s="3" t="inlineStr">
-        <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
+      <c r="F324" s="3" t="n"/>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
+          <t>ג לייה</t>
         </is>
       </c>
       <c r="H324" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
-      <c r="I324" s="3" t="inlineStr">
-        <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
+          <t>ג דניאל</t>
+        </is>
+      </c>
+      <c r="I324" s="3" t="n"/>
     </row>
     <row r="325">
       <c r="C325" s="2" t="inlineStr">
@@ -13183,30 +13187,22 @@
       </c>
       <c r="D325" s="3" t="inlineStr">
         <is>
-          <t>א פנינה / ◦ הדרכה</t>
-        </is>
-      </c>
-      <c r="E325" s="3" t="n"/>
-      <c r="F325" s="3" t="inlineStr">
-        <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
-      <c r="G325" s="3" t="inlineStr">
-        <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
+          <t>ב אביטל</t>
+        </is>
+      </c>
+      <c r="E325" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
+      <c r="F325" s="3" t="n"/>
+      <c r="G325" s="3" t="n"/>
       <c r="H325" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
-      <c r="I325" s="3" t="inlineStr">
-        <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="I325" s="3" t="n"/>
     </row>
     <row r="326">
       <c r="C326" s="2" t="inlineStr">
@@ -13217,30 +13213,26 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
-      <c r="E326" s="3" t="n"/>
-      <c r="F326" s="3" t="inlineStr">
-        <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="E326" s="3" t="inlineStr">
+        <is>
+          <t>א אנה</t>
+        </is>
+      </c>
+      <c r="F326" s="3" t="n"/>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
+          <t>ב יערה</t>
         </is>
       </c>
       <c r="H326" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
-      <c r="I326" s="3" t="inlineStr">
-        <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="I326" s="3" t="n"/>
     </row>
     <row r="327">
       <c r="C327" s="2" t="inlineStr">
@@ -13249,26 +13241,17 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D327" s="3" t="inlineStr">
-        <is>
-          <t>עם צופיה
- א פנינה</t>
-        </is>
-      </c>
+      <c r="D327" s="3" t="n"/>
       <c r="E327" s="3" t="n"/>
-      <c r="F327" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
+      <c r="F327" s="3" t="n"/>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
+          <t>ד מירי</t>
         </is>
       </c>
       <c r="H327" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
+          <t>ד אינס</t>
         </is>
       </c>
       <c r="I327" s="3" t="n"/>
@@ -13286,14 +13269,10 @@
         </is>
       </c>
       <c r="E328" s="3" t="n"/>
-      <c r="F328" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
+      <c r="F328" s="3" t="n"/>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
+          <t>ב אביטל</t>
         </is>
       </c>
       <c r="H328" s="3" t="n"/>
@@ -13320,7 +13299,7 @@
     <row r="331">
       <c r="C331" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה צבי טולצ'ינסקי</t>
+          <t>מערכת שעות למורה פנינה קרפטי</t>
         </is>
       </c>
     </row>
@@ -13381,24 +13360,30 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D334" s="3" t="n"/>
-      <c r="E334" s="3" t="inlineStr">
-        <is>
-          <t>מתמטיקה (עם הילה)
- ח גלית</t>
-        </is>
-      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="n"/>
       <c r="F334" s="3" t="inlineStr">
         <is>
-          <t>משחקי חשיבה
- ד מירי</t>
-        </is>
-      </c>
-      <c r="G334" s="3" t="n"/>
-      <c r="H334" s="3" t="n"/>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="G334" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="H334" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
       <c r="I334" s="3" t="inlineStr">
         <is>
-          <t>ט אסיף</t>
+          <t>א פנינה</t>
         </is>
       </c>
     </row>
@@ -13409,25 +13394,30 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D335" s="3" t="n"/>
-      <c r="E335" s="3" t="inlineStr">
-        <is>
-          <t>מתמטיקה (עם הילה)
- ח גלית</t>
-        </is>
-      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>◦ הדרכת שפה (קטיה)</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="n"/>
       <c r="F335" s="3" t="inlineStr">
         <is>
-          <t>מתמטיקה (עם הילה)
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="G335" s="3" t="n"/>
-      <c r="H335" s="3" t="n"/>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="G335" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="H335" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
       <c r="I335" s="3" t="inlineStr">
         <is>
-          <t>שירה בציבור
- ט אסיף</t>
+          <t>א פנינה</t>
         </is>
       </c>
     </row>
@@ -13438,24 +13428,30 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D336" s="3" t="n"/>
-      <c r="E336" s="3" t="inlineStr">
-        <is>
-          <t>משחקי חשיבה
- ד אינס</t>
-        </is>
-      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה / ◦ הדרכה</t>
+        </is>
+      </c>
+      <c r="E336" s="3" t="n"/>
       <c r="F336" s="3" t="inlineStr">
         <is>
-          <t>משחקי חשיבה
- ג דניאל</t>
-        </is>
-      </c>
-      <c r="G336" s="3" t="n"/>
-      <c r="H336" s="3" t="n"/>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="G336" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="H336" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
       <c r="I336" s="3" t="inlineStr">
         <is>
-          <t>ט אסיף</t>
+          <t>א פנינה</t>
         </is>
       </c>
     </row>
@@ -13466,24 +13462,30 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D337" s="3" t="n"/>
-      <c r="E337" s="3" t="inlineStr">
-        <is>
-          <t>משחקי חשיבה
- ג לייה</t>
-        </is>
-      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="n"/>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>מתמטיקה (עם הילה)
- ט אסיף</t>
-        </is>
-      </c>
-      <c r="G337" s="3" t="n"/>
-      <c r="H337" s="3" t="n"/>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="G337" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="H337" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
       <c r="I337" s="3" t="inlineStr">
         <is>
-          <t>ט אסיף</t>
+          <t>א פנינה</t>
         </is>
       </c>
     </row>
@@ -13494,16 +13496,28 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D338" s="3" t="n"/>
+      <c r="D338" s="3" t="inlineStr">
+        <is>
+          <t>עם צופיה
+ א פנינה</t>
+        </is>
+      </c>
       <c r="E338" s="3" t="n"/>
       <c r="F338" s="3" t="inlineStr">
         <is>
-          <t>משחקי חשיבה
- ג דליה</t>
-        </is>
-      </c>
-      <c r="G338" s="3" t="n"/>
-      <c r="H338" s="3" t="n"/>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="G338" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="H338" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
       <c r="I338" s="3" t="n"/>
     </row>
     <row r="339">
@@ -13521,11 +13535,14 @@
       <c r="E339" s="3" t="n"/>
       <c r="F339" s="3" t="inlineStr">
         <is>
-          <t>מתמטיקה (עם הילה)
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="G339" s="3" t="n"/>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="G339" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
       <c r="H339" s="3" t="n"/>
       <c r="I339" s="3" t="n"/>
     </row>
@@ -13550,7 +13567,7 @@
     <row r="342">
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה צופיה חזון</t>
+          <t>מערכת שעות למורה צבי טולצ'ינסקי</t>
         </is>
       </c>
     </row>
@@ -13611,23 +13628,24 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D345" s="3" t="inlineStr">
-        <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
-      <c r="E345" s="3" t="n"/>
+      <c r="D345" s="3" t="n"/>
+      <c r="E345" s="3" t="inlineStr">
+        <is>
+          <t>מתמטיקה (עם הילה)
+ ח גלית</t>
+        </is>
+      </c>
       <c r="F345" s="3" t="inlineStr">
         <is>
-          <t>עם אנה
- א אנה</t>
+          <t>משחקי חשיבה
+ ד מירי</t>
         </is>
       </c>
       <c r="G345" s="3" t="n"/>
       <c r="H345" s="3" t="n"/>
       <c r="I345" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>ט אסיף</t>
         </is>
       </c>
     </row>
@@ -13638,23 +13656,25 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D346" s="3" t="inlineStr">
-        <is>
-          <t>◦ הדרכת שפה (קטיה)</t>
-        </is>
-      </c>
-      <c r="E346" s="3" t="n"/>
+      <c r="D346" s="3" t="n"/>
+      <c r="E346" s="3" t="inlineStr">
+        <is>
+          <t>מתמטיקה (עם הילה)
+ ח גלית</t>
+        </is>
+      </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>עם אנה
- א אנה</t>
+          <t>מתמטיקה (עם הילה)
+ ט תמיר</t>
         </is>
       </c>
       <c r="G346" s="3" t="n"/>
       <c r="H346" s="3" t="n"/>
       <c r="I346" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>שירה בציבור
+ ט אסיף</t>
         </is>
       </c>
     </row>
@@ -13668,23 +13688,21 @@
       <c r="D347" s="3" t="n"/>
       <c r="E347" s="3" t="inlineStr">
         <is>
-          <t>ג דליה</t>
+          <t>משחקי חשיבה
+ ד אינס</t>
         </is>
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
-          <t>◦ ישיבת מרכזי בית חינוך</t>
-        </is>
-      </c>
-      <c r="G347" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+          <t>משחקי חשיבה
+ ג דניאל</t>
+        </is>
+      </c>
+      <c r="G347" s="3" t="n"/>
       <c r="H347" s="3" t="n"/>
       <c r="I347" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>ט אסיף</t>
         </is>
       </c>
     </row>
@@ -13695,30 +13713,24 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D348" s="3" t="inlineStr">
-        <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
+      <c r="D348" s="3" t="n"/>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>ג דניאל</t>
+          <t>משחקי חשיבה
+ ג לייה</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr">
         <is>
-          <t>◦ ישיבת מרכזי בית חינוך</t>
-        </is>
-      </c>
-      <c r="G348" s="3" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
+          <t>מתמטיקה (עם הילה)
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="G348" s="3" t="n"/>
       <c r="H348" s="3" t="n"/>
       <c r="I348" s="3" t="inlineStr">
         <is>
-          <t>א אנה</t>
+          <t>ט אסיף</t>
         </is>
       </c>
     </row>
@@ -13729,23 +13741,15 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D349" s="3" t="inlineStr">
-        <is>
-          <t>עם פנינה
- א פנינה</t>
-        </is>
-      </c>
+      <c r="D349" s="3" t="n"/>
       <c r="E349" s="3" t="n"/>
       <c r="F349" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
-      <c r="G349" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+          <t>משחקי חשיבה
+ ג דליה</t>
+        </is>
+      </c>
+      <c r="G349" s="3" t="n"/>
       <c r="H349" s="3" t="n"/>
       <c r="I349" s="3" t="n"/>
     </row>
@@ -13761,21 +13765,14 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E350" s="3" t="inlineStr">
-        <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
+      <c r="E350" s="3" t="n"/>
       <c r="F350" s="3" t="inlineStr">
         <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
-      <c r="G350" s="3" t="inlineStr">
-        <is>
-          <t>ג דניאל</t>
-        </is>
-      </c>
+          <t>מתמטיקה (עם הילה)
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="G350" s="3" t="n"/>
       <c r="H350" s="3" t="n"/>
       <c r="I350" s="3" t="n"/>
     </row>
@@ -13800,7 +13797,7 @@
     <row r="353">
       <c r="C353" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה רובי קיסוס</t>
+          <t>מערכת שעות למורה צופיה חזון</t>
         </is>
       </c>
     </row>
@@ -13861,17 +13858,25 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D356" s="3" t="n"/>
+      <c r="D356" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
       <c r="E356" s="3" t="n"/>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>מגמת אומנויות
- במקביל: חסן (ליווי מגמה ימית) · שרית (בישול וספורט אתגרי) · אסיף (חדשנות וטכנולוגיה)</t>
+          <t>עם אנה
+ א אנה</t>
         </is>
       </c>
       <c r="G356" s="3" t="n"/>
       <c r="H356" s="3" t="n"/>
-      <c r="I356" s="3" t="n"/>
+      <c r="I356" s="3" t="inlineStr">
+        <is>
+          <t>א אנה</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="C357" s="2" t="inlineStr">
@@ -13880,17 +13885,25 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D357" s="3" t="n"/>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>◦ הדרכת שפה (קטיה)</t>
+        </is>
+      </c>
       <c r="E357" s="3" t="n"/>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>מגמת אומנויות
- במקביל: חסן (ליווי מגמה ימית) · שרית (בישול וספורט אתגרי) · אסיף (חדשנות וטכנולוגיה)</t>
+          <t>עם אנה
+ א אנה</t>
         </is>
       </c>
       <c r="G357" s="3" t="n"/>
       <c r="H357" s="3" t="n"/>
-      <c r="I357" s="3" t="n"/>
+      <c r="I357" s="3" t="inlineStr">
+        <is>
+          <t>א אנה</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="C358" s="2" t="inlineStr">
@@ -13900,11 +13913,27 @@
         </is>
       </c>
       <c r="D358" s="3" t="n"/>
-      <c r="E358" s="3" t="n"/>
-      <c r="F358" s="3" t="n"/>
-      <c r="G358" s="3" t="n"/>
+      <c r="E358" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="F358" s="3" t="inlineStr">
+        <is>
+          <t>◦ ישיבת מרכזי בית חינוך</t>
+        </is>
+      </c>
+      <c r="G358" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="H358" s="3" t="n"/>
-      <c r="I358" s="3" t="n"/>
+      <c r="I358" s="3" t="inlineStr">
+        <is>
+          <t>א אנה</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="C359" s="2" t="inlineStr">
@@ -13913,12 +13942,32 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D359" s="3" t="n"/>
-      <c r="E359" s="3" t="n"/>
-      <c r="F359" s="3" t="n"/>
-      <c r="G359" s="3" t="n"/>
+      <c r="D359" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
+      <c r="E359" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
+      <c r="F359" s="3" t="inlineStr">
+        <is>
+          <t>◦ ישיבת מרכזי בית חינוך</t>
+        </is>
+      </c>
+      <c r="G359" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
       <c r="H359" s="3" t="n"/>
-      <c r="I359" s="3" t="n"/>
+      <c r="I359" s="3" t="inlineStr">
+        <is>
+          <t>א אנה</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="C360" s="2" t="inlineStr">
@@ -13927,10 +13976,23 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D360" s="3" t="n"/>
+      <c r="D360" s="3" t="inlineStr">
+        <is>
+          <t>עם פנינה
+ א פנינה</t>
+        </is>
+      </c>
       <c r="E360" s="3" t="n"/>
-      <c r="F360" s="3" t="n"/>
-      <c r="G360" s="3" t="n"/>
+      <c r="F360" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="G360" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="H360" s="3" t="n"/>
       <c r="I360" s="3" t="n"/>
     </row>
@@ -13946,9 +14008,21 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E361" s="3" t="n"/>
-      <c r="F361" s="3" t="n"/>
-      <c r="G361" s="3" t="n"/>
+      <c r="E361" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="F361" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
+      <c r="G361" s="3" t="inlineStr">
+        <is>
+          <t>ג דניאל</t>
+        </is>
+      </c>
       <c r="H361" s="3" t="n"/>
       <c r="I361" s="3" t="n"/>
     </row>
@@ -13973,7 +14047,7 @@
     <row r="364">
       <c r="C364" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה שחר שלייסר</t>
+          <t>מערכת שעות למורה רובי קיסוס</t>
         </is>
       </c>
     </row>
@@ -14035,17 +14109,14 @@
         </is>
       </c>
       <c r="D367" s="3" t="n"/>
-      <c r="E367" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="F367" s="3" t="n"/>
-      <c r="G367" s="3" t="inlineStr">
-        <is>
-          <t>ג לייה</t>
-        </is>
-      </c>
+      <c r="E367" s="3" t="n"/>
+      <c r="F367" s="3" t="inlineStr">
+        <is>
+          <t>מגמת אומנויות
+ במקביל: חסן (ליווי מגמה ימית) · שרית (בישול וספורט אתגרי) · אסיף (חדשנות וטכנולוגיה)</t>
+        </is>
+      </c>
+      <c r="G367" s="3" t="n"/>
       <c r="H367" s="3" t="n"/>
       <c r="I367" s="3" t="n"/>
     </row>
@@ -14058,12 +14129,13 @@
       </c>
       <c r="D368" s="3" t="n"/>
       <c r="E368" s="3" t="n"/>
-      <c r="F368" s="3" t="n"/>
-      <c r="G368" s="3" t="inlineStr">
-        <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
+      <c r="F368" s="3" t="inlineStr">
+        <is>
+          <t>מגמת אומנויות
+ במקביל: חסן (ליווי מגמה ימית) · שרית (בישול וספורט אתגרי) · אסיף (חדשנות וטכנולוגיה)</t>
+        </is>
+      </c>
+      <c r="G368" s="3" t="n"/>
       <c r="H368" s="3" t="n"/>
       <c r="I368" s="3" t="n"/>
     </row>
@@ -14075,11 +14147,7 @@
         </is>
       </c>
       <c r="D369" s="3" t="n"/>
-      <c r="E369" s="3" t="inlineStr">
-        <is>
-          <t>א פנינה</t>
-        </is>
-      </c>
+      <c r="E369" s="3" t="n"/>
       <c r="F369" s="3" t="n"/>
       <c r="G369" s="3" t="n"/>
       <c r="H369" s="3" t="n"/>
@@ -14093,21 +14161,9 @@
         </is>
       </c>
       <c r="D370" s="3" t="n"/>
-      <c r="E370" s="3" t="inlineStr">
-        <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
-      <c r="F370" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="G370" s="3" t="inlineStr">
-        <is>
-          <t>ג דליה</t>
-        </is>
-      </c>
+      <c r="E370" s="3" t="n"/>
+      <c r="F370" s="3" t="n"/>
+      <c r="G370" s="3" t="n"/>
       <c r="H370" s="3" t="n"/>
       <c r="I370" s="3" t="n"/>
     </row>
@@ -14119,21 +14175,9 @@
         </is>
       </c>
       <c r="D371" s="3" t="n"/>
-      <c r="E371" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="F371" s="3" t="inlineStr">
-        <is>
-          <t>ב יערה</t>
-        </is>
-      </c>
-      <c r="G371" s="3" t="inlineStr">
-        <is>
-          <t>ב אביטל</t>
-        </is>
-      </c>
+      <c r="E371" s="3" t="n"/>
+      <c r="F371" s="3" t="n"/>
+      <c r="G371" s="3" t="n"/>
       <c r="H371" s="3" t="n"/>
       <c r="I371" s="3" t="n"/>
     </row>
@@ -14176,7 +14220,7 @@
     <row r="375">
       <c r="C375" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה שיר אופיר</t>
+          <t>מערכת שעות למורה שחר שלייסר</t>
         </is>
       </c>
     </row>
@@ -14238,16 +14282,19 @@
         </is>
       </c>
       <c r="D378" s="3" t="n"/>
-      <c r="E378" s="3" t="n"/>
+      <c r="E378" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
       <c r="F378" s="3" t="n"/>
-      <c r="G378" s="3" t="n"/>
+      <c r="G378" s="3" t="inlineStr">
+        <is>
+          <t>ג לייה</t>
+        </is>
+      </c>
       <c r="H378" s="3" t="n"/>
-      <c r="I378" s="3" t="inlineStr">
-        <is>
-          <t>ספרות
- ז נעמי</t>
-        </is>
-      </c>
+      <c r="I378" s="3" t="n"/>
     </row>
     <row r="379">
       <c r="C379" s="2" t="inlineStr">
@@ -14259,14 +14306,13 @@
       <c r="D379" s="3" t="n"/>
       <c r="E379" s="3" t="n"/>
       <c r="F379" s="3" t="n"/>
-      <c r="G379" s="3" t="n"/>
+      <c r="G379" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
       <c r="H379" s="3" t="n"/>
-      <c r="I379" s="3" t="inlineStr">
-        <is>
-          <t>שירה בציבור
- ז אלי</t>
-        </is>
-      </c>
+      <c r="I379" s="3" t="n"/>
     </row>
     <row r="380">
       <c r="C380" s="2" t="inlineStr">
@@ -14276,16 +14322,15 @@
         </is>
       </c>
       <c r="D380" s="3" t="n"/>
-      <c r="E380" s="3" t="n"/>
+      <c r="E380" s="3" t="inlineStr">
+        <is>
+          <t>א פנינה</t>
+        </is>
+      </c>
       <c r="F380" s="3" t="n"/>
       <c r="G380" s="3" t="n"/>
       <c r="H380" s="3" t="n"/>
-      <c r="I380" s="3" t="inlineStr">
-        <is>
-          <t>ספרות
- ז אלי</t>
-        </is>
-      </c>
+      <c r="I380" s="3" t="n"/>
     </row>
     <row r="381">
       <c r="C381" s="2" t="inlineStr">
@@ -14295,16 +14340,23 @@
         </is>
       </c>
       <c r="D381" s="3" t="n"/>
-      <c r="E381" s="3" t="n"/>
-      <c r="F381" s="3" t="n"/>
-      <c r="G381" s="3" t="n"/>
+      <c r="E381" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
+      <c r="F381" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="G381" s="3" t="inlineStr">
+        <is>
+          <t>ג דליה</t>
+        </is>
+      </c>
       <c r="H381" s="3" t="n"/>
-      <c r="I381" s="3" t="inlineStr">
-        <is>
-          <t>ספרות
- ז אלי</t>
-        </is>
-      </c>
+      <c r="I381" s="3" t="n"/>
     </row>
     <row r="382">
       <c r="C382" s="2" t="inlineStr">
@@ -14314,9 +14366,21 @@
         </is>
       </c>
       <c r="D382" s="3" t="n"/>
-      <c r="E382" s="3" t="n"/>
-      <c r="F382" s="3" t="n"/>
-      <c r="G382" s="3" t="n"/>
+      <c r="E382" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="F382" s="3" t="inlineStr">
+        <is>
+          <t>ב יערה</t>
+        </is>
+      </c>
+      <c r="G382" s="3" t="inlineStr">
+        <is>
+          <t>ב אביטל</t>
+        </is>
+      </c>
       <c r="H382" s="3" t="n"/>
       <c r="I382" s="3" t="n"/>
     </row>
@@ -14359,7 +14423,7 @@
     <row r="386">
       <c r="C386" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה שרית גונן</t>
+          <t>מערכת שעות למורה שיר אופיר</t>
         </is>
       </c>
     </row>
@@ -14420,31 +14484,15 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D389" s="3" t="inlineStr">
-        <is>
-          <t>◦ הדרכת עברית (קטיה)</t>
-        </is>
-      </c>
-      <c r="E389" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="F389" s="3" t="inlineStr">
-        <is>
-          <t>מגמת בישול וספורט אתגרי
- במקביל: חסן (ליווי מגמה ימית) · רובי (אומנויות) · אסיף (חדשנות וטכנולוגיה)</t>
-        </is>
-      </c>
-      <c r="G389" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
+      <c r="D389" s="3" t="n"/>
+      <c r="E389" s="3" t="n"/>
+      <c r="F389" s="3" t="n"/>
+      <c r="G389" s="3" t="n"/>
       <c r="H389" s="3" t="n"/>
       <c r="I389" s="3" t="inlineStr">
         <is>
-          <t>ו שרית</t>
+          <t>ספרות
+ ז נעמי</t>
         </is>
       </c>
     </row>
@@ -14455,33 +14503,15 @@
  8:45-9:30</t>
         </is>
       </c>
-      <c r="D390" s="3" t="inlineStr">
-        <is>
-          <t>חינוך גופני
- ז נעמי / חינוך גופני
- ז אלי</t>
-        </is>
-      </c>
-      <c r="E390" s="3" t="inlineStr">
-        <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="F390" s="3" t="inlineStr">
-        <is>
-          <t>מגמת בישול וספורט אתגרי
- במקביל: חסן (ליווי מגמה ימית) · רובי (אומנויות) · אסיף (חדשנות וטכנולוגיה)</t>
-        </is>
-      </c>
-      <c r="G390" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
+      <c r="D390" s="3" t="n"/>
+      <c r="E390" s="3" t="n"/>
+      <c r="F390" s="3" t="n"/>
+      <c r="G390" s="3" t="n"/>
       <c r="H390" s="3" t="n"/>
       <c r="I390" s="3" t="inlineStr">
         <is>
-          <t>ו שרית</t>
+          <t>שירה בציבור
+ ז אלי</t>
         </is>
       </c>
     </row>
@@ -14492,32 +14522,15 @@
  9:40-10:25</t>
         </is>
       </c>
-      <c r="D391" s="3" t="inlineStr">
-        <is>
-          <t>חינוך גופני
- ט תמיר / חינוך גופני
- ט אסיף</t>
-        </is>
-      </c>
-      <c r="E391" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="F391" s="3" t="inlineStr">
-        <is>
-          <t>◦ ישיבת מרכזי בית חינוך</t>
-        </is>
-      </c>
-      <c r="G391" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
+      <c r="D391" s="3" t="n"/>
+      <c r="E391" s="3" t="n"/>
+      <c r="F391" s="3" t="n"/>
+      <c r="G391" s="3" t="n"/>
       <c r="H391" s="3" t="n"/>
       <c r="I391" s="3" t="inlineStr">
         <is>
-          <t>ו שרית</t>
+          <t>ספרות
+ ז אלי</t>
         </is>
       </c>
     </row>
@@ -14528,32 +14541,15 @@
  10:25-11:10</t>
         </is>
       </c>
-      <c r="D392" s="3" t="inlineStr">
-        <is>
-          <t>חינוך גופני
- ח גלית</t>
-        </is>
-      </c>
-      <c r="E392" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="F392" s="3" t="inlineStr">
-        <is>
-          <t>◦ ישיבת מרכזי בית חינוך</t>
-        </is>
-      </c>
-      <c r="G392" s="3" t="inlineStr">
-        <is>
-          <t>חינוך גופני
- ח גלית</t>
-        </is>
-      </c>
+      <c r="D392" s="3" t="n"/>
+      <c r="E392" s="3" t="n"/>
+      <c r="F392" s="3" t="n"/>
+      <c r="G392" s="3" t="n"/>
       <c r="H392" s="3" t="n"/>
       <c r="I392" s="3" t="inlineStr">
         <is>
-          <t>ו שרית</t>
+          <t>ספרות
+ ז אלי</t>
         </is>
       </c>
     </row>
@@ -14564,28 +14560,10 @@
  11:30-12:15</t>
         </is>
       </c>
-      <c r="D393" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="E393" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="F393" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="G393" s="3" t="inlineStr">
-        <is>
-          <t>חינוך גופני
- ז נעמי / חינוך גופני
- ז אלי</t>
-        </is>
-      </c>
+      <c r="D393" s="3" t="n"/>
+      <c r="E393" s="3" t="n"/>
+      <c r="F393" s="3" t="n"/>
+      <c r="G393" s="3" t="n"/>
       <c r="H393" s="3" t="n"/>
       <c r="I393" s="3" t="n"/>
     </row>
@@ -14601,23 +14579,9 @@
           <t>◦ אסיפת צוות</t>
         </is>
       </c>
-      <c r="E394" s="3" t="inlineStr">
-        <is>
-          <t>ו שרית</t>
-        </is>
-      </c>
-      <c r="F394" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="G394" s="3" t="inlineStr">
-        <is>
-          <t>חינוך גופני
- ט תמיר / חינוך גופני
- ט אסיף</t>
-        </is>
-      </c>
+      <c r="E394" s="3" t="n"/>
+      <c r="F394" s="3" t="n"/>
+      <c r="G394" s="3" t="n"/>
       <c r="H394" s="3" t="n"/>
       <c r="I394" s="3" t="n"/>
     </row>
@@ -14642,7 +14606,7 @@
     <row r="397">
       <c r="C397" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה תמיר באום</t>
+          <t>מערכת שעות למורה שרית גונן</t>
         </is>
       </c>
     </row>
@@ -14705,30 +14669,29 @@
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
+          <t>◦ הדרכת עברית (קטיה)</t>
+        </is>
+      </c>
+      <c r="E400" s="3" t="inlineStr">
+        <is>
           <t>ו אורנה</t>
         </is>
       </c>
-      <c r="E400" s="3" t="inlineStr">
-        <is>
-          <t>תנ"ך
- ט אסיף</t>
-        </is>
-      </c>
-      <c r="F400" s="3" t="n"/>
+      <c r="F400" s="3" t="inlineStr">
+        <is>
+          <t>מגמת בישול וספורט אתגרי
+ במקביל: חסן (ליווי מגמה ימית) · רובי (אומנויות) · אסיף (חדשנות וטכנולוגיה)</t>
+        </is>
+      </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>ו אורנה</t>
-        </is>
-      </c>
-      <c r="H400" s="3" t="inlineStr">
-        <is>
-          <t>מגמת ימאות
- במקביל: אסיף (יזמות) · מאמי (אומנות בתנועה) · חסן (ספורט)</t>
-        </is>
-      </c>
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="H400" s="3" t="n"/>
       <c r="I400" s="3" t="inlineStr">
         <is>
-          <t>ט תמיר</t>
+          <t>ו שרית</t>
         </is>
       </c>
     </row>
@@ -14741,32 +14704,31 @@
       </c>
       <c r="D401" s="3" t="inlineStr">
         <is>
+          <t>חינוך גופני
+ ז נעמי / חינוך גופני
+ ז אלי</t>
+        </is>
+      </c>
+      <c r="E401" s="3" t="inlineStr">
+        <is>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="F401" s="3" t="inlineStr">
+        <is>
+          <t>מגמת בישול וספורט אתגרי
+ במקביל: חסן (ליווי מגמה ימית) · רובי (אומנויות) · אסיף (חדשנות וטכנולוגיה)</t>
+        </is>
+      </c>
+      <c r="G401" s="3" t="inlineStr">
+        <is>
           <t>ו שרית</t>
         </is>
       </c>
-      <c r="E401" s="3" t="inlineStr">
-        <is>
-          <t>אזרחות
- ט אסיף</t>
-        </is>
-      </c>
-      <c r="F401" s="3" t="n"/>
-      <c r="G401" s="3" t="inlineStr">
-        <is>
-          <t>אזרחות
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="H401" s="3" t="inlineStr">
-        <is>
-          <t>מגמת ימאות
- במקביל: אסיף (יזמות) · מאמי (אומנות בתנועה) · חסן (ספורט)</t>
-        </is>
-      </c>
+      <c r="H401" s="3" t="n"/>
       <c r="I401" s="3" t="inlineStr">
         <is>
-          <t>שירה בציבור
- ט תמיר</t>
+          <t>ו שרית</t>
         </is>
       </c>
     </row>
@@ -14779,31 +14741,30 @@
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
+          <t>חינוך גופני
+ ט תמיר / חינוך גופני
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="E402" s="3" t="inlineStr">
+        <is>
           <t>ו שרית</t>
         </is>
       </c>
-      <c r="E402" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח) / ◦ פגישות הנהלה</t>
-        </is>
-      </c>
-      <c r="F402" s="3" t="n"/>
+      <c r="F402" s="3" t="inlineStr">
+        <is>
+          <t>◦ ישיבת מרכזי בית חינוך</t>
+        </is>
+      </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך
- ט אסיף</t>
-        </is>
-      </c>
-      <c r="H402" s="3" t="inlineStr">
-        <is>
-          <t>מגמת ליווי כדורעף
- במקביל: אלי (יזמות) · מאמי (אומנות בתנועה) · יעל (תזונה)</t>
-        </is>
-      </c>
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="H402" s="3" t="n"/>
       <c r="I402" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך
- ט תמיר</t>
+          <t>ו שרית</t>
         </is>
       </c>
     </row>
@@ -14816,32 +14777,30 @@
       </c>
       <c r="D403" s="3" t="inlineStr">
         <is>
-          <t>אזרחות
- ט אסיף</t>
+          <t>חינוך גופני
+ ח גלית</t>
         </is>
       </c>
       <c r="E403" s="3" t="inlineStr">
         <is>
-          <t>◦ מפגשה (מעגלי שיח) / ◦ פגישות הנהלה</t>
-        </is>
-      </c>
-      <c r="F403" s="3" t="n"/>
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="F403" s="3" t="inlineStr">
+        <is>
+          <t>◦ ישיבת מרכזי בית חינוך</t>
+        </is>
+      </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>חינוך
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="H403" s="3" t="inlineStr">
-        <is>
-          <t>מגמת ליווי כדורעף
- במקביל: אלי (יזמות) · מאמי (אומנות בתנועה) · יעל (תזונה)</t>
-        </is>
-      </c>
+          <t>חינוך גופני
+ ח גלית</t>
+        </is>
+      </c>
+      <c r="H403" s="3" t="n"/>
       <c r="I403" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה
- ט תמיר</t>
+          <t>ו שרית</t>
         </is>
       </c>
     </row>
@@ -14854,29 +14813,27 @@
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>אזרחות
- ט תמיר</t>
+          <t>ו שרית</t>
         </is>
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>תנ"ך
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="F404" s="3" t="n"/>
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="F404" s="3" t="inlineStr">
+        <is>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה
- ט תמיר</t>
-        </is>
-      </c>
-      <c r="H404" s="3" t="inlineStr">
-        <is>
-          <t>חינוך
- ט תמיר</t>
-        </is>
-      </c>
+          <t>חינוך גופני
+ ז נעמי / חינוך גופני
+ ז אלי</t>
+        </is>
+      </c>
+      <c r="H404" s="3" t="n"/>
       <c r="I404" s="3" t="n"/>
     </row>
     <row r="405">
@@ -14893,14 +14850,19 @@
       </c>
       <c r="E405" s="3" t="inlineStr">
         <is>
-          <t>היסטוריה
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="F405" s="3" t="inlineStr">
+        <is>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="G405" s="3" t="inlineStr">
+        <is>
+          <t>חינוך גופני
+ ט תמיר / חינוך גופני
  ט אסיף</t>
-        </is>
-      </c>
-      <c r="F405" s="3" t="n"/>
-      <c r="G405" s="3" t="inlineStr">
-        <is>
-          <t>◦ ישיבת צוות חטיבה</t>
         </is>
       </c>
       <c r="H405" s="3" t="n"/>
@@ -14927,7 +14889,7 @@
     <row r="408">
       <c r="C408" s="1" t="inlineStr">
         <is>
-          <t>מערכת שעות למורה תניה דניאלי</t>
+          <t>מערכת שעות למורה תמיר באום</t>
         </is>
       </c>
     </row>
@@ -14990,28 +14952,30 @@
       </c>
       <c r="D411" s="3" t="inlineStr">
         <is>
-          <t>◦ מתחילה ב-10:00</t>
+          <t>ו אורנה</t>
         </is>
       </c>
       <c r="E411" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="F411" s="3" t="inlineStr">
-        <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
+          <t>תנ"ך
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="F411" s="3" t="n"/>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>◦ מתחילה ב-10:00</t>
-        </is>
-      </c>
-      <c r="H411" s="3" t="n"/>
+          <t>ו אורנה</t>
+        </is>
+      </c>
+      <c r="H411" s="3" t="inlineStr">
+        <is>
+          <t>מגמת ימאות
+ במקביל: אסיף (יזמות) · מאמי (אומנות בתנועה) · חסן (ספורט)</t>
+        </is>
+      </c>
       <c r="I411" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
+          <t>ט תמיר</t>
         </is>
       </c>
     </row>
@@ -15024,24 +14988,32 @@
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>◦ מתחילה ב-10:00</t>
-        </is>
-      </c>
-      <c r="E412" s="3" t="n"/>
-      <c r="F412" s="3" t="inlineStr">
-        <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
+          <t>ו שרית</t>
+        </is>
+      </c>
+      <c r="E412" s="3" t="inlineStr">
+        <is>
+          <t>אזרחות
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="F412" s="3" t="n"/>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>◦ מתחילה ב-10:00</t>
-        </is>
-      </c>
-      <c r="H412" s="3" t="n"/>
+          <t>אזרחות
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="H412" s="3" t="inlineStr">
+        <is>
+          <t>מגמת ימאות
+ במקביל: אסיף (יזמות) · מאמי (אומנות בתנועה) · חסן (ספורט)</t>
+        </is>
+      </c>
       <c r="I412" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
+          <t>שירה בציבור
+ ט תמיר</t>
         </is>
       </c>
     </row>
@@ -15054,28 +15026,31 @@
       </c>
       <c r="D413" s="3" t="inlineStr">
         <is>
-          <t>שיעור הדרכה</t>
+          <t>ו שרית</t>
         </is>
       </c>
       <c r="E413" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="F413" s="3" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
+          <t>◦ מפגשה (מעגלי שיח) / ◦ פגישות הנהלה</t>
+        </is>
+      </c>
+      <c r="F413" s="3" t="n"/>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="H413" s="3" t="n"/>
+          <t>תנ"ך
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="H413" s="3" t="inlineStr">
+        <is>
+          <t>מגמת ליווי כדורעף
+ במקביל: אלי (יזמות) · מאמי (אומנות בתנועה) · יעל (תזונה)</t>
+        </is>
+      </c>
       <c r="I413" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
+          <t>תנ"ך
+ ט תמיר</t>
         </is>
       </c>
     </row>
@@ -15088,28 +15063,32 @@
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
+          <t>אזרחות
+ ט אסיף</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>ה דני</t>
-        </is>
-      </c>
-      <c r="F414" s="3" t="inlineStr">
-        <is>
-          <t>ה דני</t>
-        </is>
-      </c>
+          <t>◦ מפגשה (מעגלי שיח) / ◦ פגישות הנהלה</t>
+        </is>
+      </c>
+      <c r="F414" s="3" t="n"/>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="H414" s="3" t="n"/>
+          <t>חינוך
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="H414" s="3" t="inlineStr">
+        <is>
+          <t>מגמת ליווי כדורעף
+ במקביל: אלי (יזמות) · מאמי (אומנות בתנועה) · יעל (תזונה)</t>
+        </is>
+      </c>
       <c r="I414" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
+          <t>היסטוריה
+ ט תמיר</t>
         </is>
       </c>
     </row>
@@ -15122,21 +15101,29 @@
       </c>
       <c r="D415" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="E415" s="3" t="n"/>
-      <c r="F415" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
+          <t>אזרחות
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="E415" s="3" t="inlineStr">
+        <is>
+          <t>תנ"ך
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="F415" s="3" t="n"/>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="H415" s="3" t="n"/>
+          <t>היסטוריה
+ ט תמיר</t>
+        </is>
+      </c>
+      <c r="H415" s="3" t="inlineStr">
+        <is>
+          <t>חינוך
+ ט תמיר</t>
+        </is>
+      </c>
       <c r="I415" s="3" t="n"/>
     </row>
     <row r="416">
@@ -15153,15 +15140,16 @@
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>ה תניה</t>
-        </is>
-      </c>
-      <c r="F416" s="3" t="inlineStr">
-        <is>
-          <t>◦ מפגשה (מעגלי שיח)</t>
-        </is>
-      </c>
-      <c r="G416" s="3" t="n"/>
+          <t>היסטוריה
+ ט אסיף</t>
+        </is>
+      </c>
+      <c r="F416" s="3" t="n"/>
+      <c r="G416" s="3" t="inlineStr">
+        <is>
+          <t>◦ ישיבת צוות חטיבה</t>
+        </is>
+      </c>
       <c r="H416" s="3" t="n"/>
       <c r="I416" s="3" t="n"/>
     </row>
@@ -15183,8 +15171,267 @@
       <c r="H417" s="3" t="n"/>
       <c r="I417" s="3" t="n"/>
     </row>
+    <row r="419">
+      <c r="C419" s="1" t="inlineStr">
+        <is>
+          <t>מערכת שעות למורה תניה דניאלי</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>שעה / יום</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>ראשון</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>שני</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>בוקר טוב</t>
+        </is>
+      </c>
+      <c r="D421" s="7" t="n"/>
+      <c r="E421" s="7" t="n"/>
+      <c r="F421" s="7" t="n"/>
+      <c r="G421" s="7" t="n"/>
+      <c r="H421" s="7" t="n"/>
+      <c r="I421" s="7" t="n"/>
+    </row>
+    <row r="422">
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>1
+ 8:00-8:45</t>
+        </is>
+      </c>
+      <c r="D422" s="3" t="inlineStr">
+        <is>
+          <t>◦ מתחילה ב-10:00</t>
+        </is>
+      </c>
+      <c r="E422" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="F422" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="G422" s="3" t="inlineStr">
+        <is>
+          <t>◦ מתחילה ב-10:00</t>
+        </is>
+      </c>
+      <c r="H422" s="3" t="n"/>
+      <c r="I422" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>2
+ 8:45-9:30</t>
+        </is>
+      </c>
+      <c r="D423" s="3" t="inlineStr">
+        <is>
+          <t>◦ מתחילה ב-10:00</t>
+        </is>
+      </c>
+      <c r="E423" s="3" t="n"/>
+      <c r="F423" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="G423" s="3" t="inlineStr">
+        <is>
+          <t>◦ מתחילה ב-10:00</t>
+        </is>
+      </c>
+      <c r="H423" s="3" t="n"/>
+      <c r="I423" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>3
+ 9:40-10:25</t>
+        </is>
+      </c>
+      <c r="D424" s="3" t="inlineStr">
+        <is>
+          <t>שיעור הדרכה</t>
+        </is>
+      </c>
+      <c r="E424" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="F424" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="G424" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="H424" s="3" t="n"/>
+      <c r="I424" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>4
+ 10:25-11:10</t>
+        </is>
+      </c>
+      <c r="D425" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="E425" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="F425" s="3" t="inlineStr">
+        <is>
+          <t>ה דני</t>
+        </is>
+      </c>
+      <c r="G425" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="H425" s="3" t="n"/>
+      <c r="I425" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>5
+ 11:30-12:15</t>
+        </is>
+      </c>
+      <c r="D426" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="E426" s="3" t="n"/>
+      <c r="F426" s="3" t="inlineStr">
+        <is>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="G426" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="H426" s="3" t="n"/>
+      <c r="I426" s="3" t="n"/>
+    </row>
+    <row r="427">
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>6
+ 12:35-13:20</t>
+        </is>
+      </c>
+      <c r="D427" s="3" t="inlineStr">
+        <is>
+          <t>◦ אסיפת צוות</t>
+        </is>
+      </c>
+      <c r="E427" s="3" t="inlineStr">
+        <is>
+          <t>ה תניה</t>
+        </is>
+      </c>
+      <c r="F427" s="3" t="inlineStr">
+        <is>
+          <t>◦ מפגשה (מעגלי שיח)</t>
+        </is>
+      </c>
+      <c r="G427" s="3" t="n"/>
+      <c r="H427" s="3" t="n"/>
+      <c r="I427" s="3" t="n"/>
+    </row>
+    <row r="428">
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>7
+ 13:20-14:05</t>
+        </is>
+      </c>
+      <c r="D428" s="3" t="inlineStr">
+        <is>
+          <t>◦ אסיפת צוות</t>
+        </is>
+      </c>
+      <c r="E428" s="3" t="n"/>
+      <c r="F428" s="3" t="n"/>
+      <c r="G428" s="3" t="n"/>
+      <c r="H428" s="3" t="n"/>
+      <c r="I428" s="3" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="39">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C221:E221"/>
     <mergeCell ref="C177:E177"/>
@@ -15212,6 +15459,7 @@
     <mergeCell ref="C254:E254"/>
     <mergeCell ref="C78:E78"/>
     <mergeCell ref="C298:E298"/>
+    <mergeCell ref="C419:E419"/>
     <mergeCell ref="C34:E34"/>
     <mergeCell ref="C166:E166"/>
     <mergeCell ref="C210:E210"/>

--- a/מערכות שעות - גורדון.xlsx
+++ b/מערכות שעות - גורדון.xlsx
@@ -1382,7 +1382,7 @@
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t>אביטל
- ½ הכיתה בתל"ן · הילית</t>
+ פינת חי · ½ הכיתה בתל"ן · הילית · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1536,8 +1536,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>אביטל
- פינת חי · + אבי קרן צבי</t>
+          <t>אביטל</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2197,8 +2196,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>צופיה
- פינת חי · + אבי קרן צבי</t>
+          <t>צופיה</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -2352,7 +2350,8 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>דליה</t>
+          <t>דליה
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -5993,7 +5992,7 @@
       <c r="D4" s="3" t="inlineStr">
         <is>
           <t>פינת חי
- ג דליה</t>
+ ב אביטל</t>
         </is>
       </c>
       <c r="E4" s="3" t="n"/>
@@ -6104,7 +6103,7 @@
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>פינת חי
- ב אביטל</t>
+ ג דליה</t>
         </is>
       </c>
       <c r="E8" s="3" t="n"/>

--- a/מערכות שעות - גורדון.xlsx
+++ b/מערכות שעות - גורדון.xlsx
@@ -1382,7 +1382,7 @@
       <c r="D24" s="3" t="inlineStr">
         <is>
           <t>אביטל
- פינת חי · ½ הכיתה בתל"ן · הילית · + אבי קרן צבי</t>
+ ½ הכיתה בתל"ן · הילית</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1420,7 +1420,8 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>אביטל</t>
+          <t>אביטל
+ פינת חי · + אבי קרן צבי</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -5989,36 +5990,36 @@
  8:00-8:45</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>פינת חי
+ א פנינה</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>פינת חי
+ ג דליה</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2
+ 8:45-9:30</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>פינת חי
  ב אביטל</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>פינת חי
- א פנינה</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>פינת חי
- ג דליה</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2
- 8:45-9:30</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>

--- a/מערכות שעות - גורדון.xlsx
+++ b/מערכות שעות - גורדון.xlsx
@@ -12210,7 +12210,7 @@
       </c>
       <c r="D283" s="3" t="inlineStr">
         <is>
-          <t>◦ הדרכת שפה (קטיה)</t>
+          <t>◦ הדרכת שפה (קטיה) / ◦ פגישה עם פסיכולוגית</t>
         </is>
       </c>
       <c r="E283" s="3" t="inlineStr">
